--- a/src/Red_Tilapia_Distribution_Cleaned.xlsx
+++ b/src/Red_Tilapia_Distribution_Cleaned.xlsx
@@ -1,15 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="23040" windowHeight="9708"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="X2QWN2/eAmjK9vjFKE94+fMHaIHQHycFx3O14C+pTnE="/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1734,36 +1745,388 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;₱&quot;* #,##0_-;\-&quot;₱&quot;* #,##0_-;_-&quot;₱&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;₱&quot;* #,##0.00_-;\-&quot;₱&quot;* #,##0.00_-;_-&quot;₱&quot;* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="23">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border/>
+  <borders count="10">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -1777,36 +2140,541 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1996,29 +2864,29 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I1000"/>
+  <sheetFormatPr defaultColWidth="14.4259259259259" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.29"/>
-    <col customWidth="1" min="2" max="2" width="27.14"/>
-    <col customWidth="1" min="3" max="3" width="39.29"/>
-    <col customWidth="1" min="4" max="4" width="16.43"/>
-    <col customWidth="1" min="5" max="5" width="14.86"/>
-    <col customWidth="1" min="6" max="6" width="10.86"/>
-    <col customWidth="1" min="7" max="7" width="12.29"/>
-    <col customWidth="1" min="8" max="8" width="16.43"/>
-    <col customWidth="1" min="9" max="9" width="18.0"/>
-    <col customWidth="1" min="10" max="26" width="9.0"/>
+    <col min="1" max="1" width="17.287037037037" customWidth="1"/>
+    <col min="2" max="2" width="27.1388888888889" customWidth="1"/>
+    <col min="3" max="3" width="39.287037037037" customWidth="1"/>
+    <col min="4" max="4" width="16.4259259259259" customWidth="1"/>
+    <col min="5" max="5" width="14.8611111111111" customWidth="1"/>
+    <col min="6" max="6" width="10.8611111111111" customWidth="1"/>
+    <col min="7" max="7" width="12.287037037037" customWidth="1"/>
+    <col min="8" max="8" width="16.4259259259259" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="26" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1">
+    <row r="1" ht="14.25" customHeight="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2047,7 +2915,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1">
+    <row r="2" ht="14.25" customHeight="1" spans="1:9">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -2064,16 +2932,16 @@
         <v>13</v>
       </c>
       <c r="F2" s="2">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="2">
-        <v>585.0</v>
-      </c>
-    </row>
-    <row r="3" ht="14.25" customHeight="1">
+      <c r="I2" s="3">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25" customHeight="1" spans="1:9">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -2090,16 +2958,16 @@
         <v>13</v>
       </c>
       <c r="F3" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25" customHeight="1">
+      <c r="I3" s="4">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" customHeight="1" spans="1:9">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -2116,16 +2984,16 @@
         <v>23</v>
       </c>
       <c r="F4" s="2">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="2">
-        <v>585.0</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25" customHeight="1">
+      <c r="I4" s="4">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" customHeight="1" spans="1:9">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -2142,16 +3010,16 @@
         <v>13</v>
       </c>
       <c r="F5" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="6" ht="14.25" customHeight="1">
+      <c r="I5" s="4">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25" customHeight="1" spans="1:9">
       <c r="A6" s="2" t="s">
         <v>27</v>
       </c>
@@ -2168,16 +3036,16 @@
         <v>13</v>
       </c>
       <c r="F6" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25" customHeight="1">
+      <c r="I6" s="4">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" customHeight="1" spans="1:9">
       <c r="A7" s="2" t="s">
         <v>27</v>
       </c>
@@ -2194,16 +3062,16 @@
         <v>13</v>
       </c>
       <c r="F7" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25" customHeight="1">
+      <c r="I7" s="4">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" customHeight="1" spans="1:9">
       <c r="A8" s="2" t="s">
         <v>33</v>
       </c>
@@ -2220,16 +3088,16 @@
         <v>13</v>
       </c>
       <c r="F8" s="2">
-        <v>10900.0</v>
+        <v>10900</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="2">
-        <v>2125.0</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25" customHeight="1">
+      <c r="I8" s="4">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25" customHeight="1" spans="1:9">
       <c r="A9" s="2" t="s">
         <v>36</v>
       </c>
@@ -2246,16 +3114,16 @@
         <v>40</v>
       </c>
       <c r="F9" s="2">
-        <v>21000.0</v>
+        <v>21000</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="2">
-        <v>4095.0</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25" customHeight="1">
+      <c r="I9" s="4">
+        <v>4051</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customHeight="1" spans="1:9">
       <c r="A10" s="2" t="s">
         <v>41</v>
       </c>
@@ -2272,16 +3140,16 @@
         <v>13</v>
       </c>
       <c r="F10" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" customHeight="1">
+      <c r="I10" s="4">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" customHeight="1" spans="1:9">
       <c r="A11" s="2" t="s">
         <v>41</v>
       </c>
@@ -2298,16 +3166,16 @@
         <v>13</v>
       </c>
       <c r="F11" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25" customHeight="1">
+      <c r="I11" s="4">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" customHeight="1" spans="1:9">
       <c r="A12" s="2" t="s">
         <v>45</v>
       </c>
@@ -2324,16 +3192,16 @@
         <v>13</v>
       </c>
       <c r="F12" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I12" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" customHeight="1">
+      <c r="I12" s="4">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" customHeight="1" spans="1:9">
       <c r="A13" s="2" t="s">
         <v>45</v>
       </c>
@@ -2350,16 +3218,16 @@
         <v>23</v>
       </c>
       <c r="F13" s="2">
-        <v>250.0</v>
+        <v>250</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I13" s="2">
-        <v>48.0</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25" customHeight="1">
+      <c r="I13" s="4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" customHeight="1" spans="1:9">
       <c r="A14" s="2" t="s">
         <v>45</v>
       </c>
@@ -2376,16 +3244,16 @@
         <v>13</v>
       </c>
       <c r="F14" s="2">
-        <v>350.0</v>
+        <v>350</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I14" s="2">
-        <v>68.0</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25" customHeight="1">
+      <c r="I14" s="4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" customHeight="1" spans="1:9">
       <c r="A15" s="2" t="s">
         <v>54</v>
       </c>
@@ -2402,16 +3270,16 @@
         <v>23</v>
       </c>
       <c r="F15" s="2">
-        <v>200.0</v>
+        <v>200</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I15" s="2">
-        <v>39.0</v>
-      </c>
-    </row>
-    <row r="16" ht="14.25" customHeight="1">
+      <c r="I15" s="4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" customHeight="1" spans="1:9">
       <c r="A16" s="2" t="s">
         <v>54</v>
       </c>
@@ -2428,16 +3296,16 @@
         <v>13</v>
       </c>
       <c r="F16" s="2">
-        <v>1500.0</v>
+        <v>1500</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I16" s="2">
-        <v>292.0</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" customHeight="1">
+      <c r="I16" s="4">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" customHeight="1" spans="1:9">
       <c r="A17" s="2" t="s">
         <v>58</v>
       </c>
@@ -2454,16 +3322,16 @@
         <v>23</v>
       </c>
       <c r="F17" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I17" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="18" ht="14.25" customHeight="1">
+      <c r="I17" s="4">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25" customHeight="1" spans="1:9">
       <c r="A18" s="2" t="s">
         <v>61</v>
       </c>
@@ -2480,16 +3348,16 @@
         <v>13</v>
       </c>
       <c r="F18" s="2">
-        <v>2500.0</v>
+        <v>2500</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="2">
-        <v>487.0</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" customHeight="1">
+      <c r="I18" s="4">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" customHeight="1" spans="1:9">
       <c r="A19" s="2" t="s">
         <v>63</v>
       </c>
@@ -2506,16 +3374,16 @@
         <v>67</v>
       </c>
       <c r="F19" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I19" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="20" ht="14.25" customHeight="1">
+      <c r="I19" s="4">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25" customHeight="1" spans="1:9">
       <c r="A20" s="2" t="s">
         <v>68</v>
       </c>
@@ -2532,16 +3400,16 @@
         <v>40</v>
       </c>
       <c r="F20" s="2">
-        <v>200.0</v>
+        <v>200</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I20" s="2">
-        <v>39.0</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" customHeight="1">
+      <c r="I20" s="4">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" customHeight="1" spans="1:9">
       <c r="A21" s="2" t="s">
         <v>68</v>
       </c>
@@ -2558,16 +3426,16 @@
         <v>13</v>
       </c>
       <c r="F21" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I21" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="22" ht="14.25" customHeight="1">
+      <c r="I21" s="4">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25" customHeight="1" spans="1:9">
       <c r="A22" s="2" t="s">
         <v>73</v>
       </c>
@@ -2584,16 +3452,16 @@
         <v>13</v>
       </c>
       <c r="F22" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I22" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" customHeight="1">
+      <c r="I22" s="4">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" customHeight="1" spans="1:9">
       <c r="A23" s="2" t="s">
         <v>77</v>
       </c>
@@ -2610,16 +3478,16 @@
         <v>81</v>
       </c>
       <c r="F23" s="2">
-        <v>40000.0</v>
+        <v>40000</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I23" s="2">
-        <v>7800.0</v>
-      </c>
-    </row>
-    <row r="24" ht="14.25" customHeight="1">
+      <c r="I23" s="4">
+        <v>7587</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25" customHeight="1" spans="1:9">
       <c r="A24" s="2" t="s">
         <v>82</v>
       </c>
@@ -2636,16 +3504,16 @@
         <v>13</v>
       </c>
       <c r="F24" s="2">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I24" s="2">
-        <v>585.0</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" customHeight="1">
+      <c r="I24" s="4">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" customHeight="1" spans="1:9">
       <c r="A25" s="2" t="s">
         <v>82</v>
       </c>
@@ -2662,16 +3530,16 @@
         <v>13</v>
       </c>
       <c r="F25" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I25" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="26" ht="14.25" customHeight="1">
+      <c r="I25" s="4">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25" customHeight="1" spans="1:9">
       <c r="A26" s="2" t="s">
         <v>82</v>
       </c>
@@ -2688,16 +3556,16 @@
         <v>13</v>
       </c>
       <c r="F26" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I26" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25" customHeight="1">
+      <c r="I26" s="4">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25" customHeight="1" spans="1:9">
       <c r="A27" s="2" t="s">
         <v>82</v>
       </c>
@@ -2714,16 +3582,16 @@
         <v>13</v>
       </c>
       <c r="F27" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I27" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="28" ht="14.25" customHeight="1">
+      <c r="I27" s="4">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25" customHeight="1" spans="1:9">
       <c r="A28" s="2" t="s">
         <v>82</v>
       </c>
@@ -2740,16 +3608,16 @@
         <v>40</v>
       </c>
       <c r="F28" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I28" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25" customHeight="1">
+      <c r="I28" s="4">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25" customHeight="1" spans="1:9">
       <c r="A29" s="2" t="s">
         <v>82</v>
       </c>
@@ -2766,16 +3634,16 @@
         <v>13</v>
       </c>
       <c r="F29" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I29" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="30" ht="14.25" customHeight="1">
+      <c r="I29" s="4">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25" customHeight="1" spans="1:9">
       <c r="A30" s="2" t="s">
         <v>93</v>
       </c>
@@ -2792,16 +3660,16 @@
         <v>13</v>
       </c>
       <c r="F30" s="2">
-        <v>15000.0</v>
+        <v>15000</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I30" s="2">
-        <v>2925.0</v>
-      </c>
-    </row>
-    <row r="31" ht="14.25" customHeight="1">
+      <c r="I30" s="4">
+        <v>2984</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25" customHeight="1" spans="1:9">
       <c r="A31" s="2" t="s">
         <v>93</v>
       </c>
@@ -2818,16 +3686,16 @@
         <v>13</v>
       </c>
       <c r="F31" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I31" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="32" ht="14.25" customHeight="1">
+      <c r="I31" s="4">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25" customHeight="1" spans="1:9">
       <c r="A32" s="2" t="s">
         <v>97</v>
       </c>
@@ -2844,16 +3712,16 @@
         <v>13</v>
       </c>
       <c r="F32" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I32" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="33" ht="14.25" customHeight="1">
+      <c r="I32" s="4">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25" customHeight="1" spans="1:9">
       <c r="A33" s="2" t="s">
         <v>97</v>
       </c>
@@ -2870,16 +3738,16 @@
         <v>13</v>
       </c>
       <c r="F33" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I33" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="34" ht="14.25" customHeight="1">
+      <c r="I33" s="4">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25" customHeight="1" spans="1:9">
       <c r="A34" s="2" t="s">
         <v>97</v>
       </c>
@@ -2896,16 +3764,16 @@
         <v>13</v>
       </c>
       <c r="F34" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I34" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="35" ht="14.25" customHeight="1">
+      <c r="I34" s="4">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25" customHeight="1" spans="1:9">
       <c r="A35" s="2" t="s">
         <v>97</v>
       </c>
@@ -2922,16 +3790,16 @@
         <v>40</v>
       </c>
       <c r="F35" s="2">
-        <v>6000.0</v>
+        <v>6000</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I35" s="2">
-        <v>1170.0</v>
-      </c>
-    </row>
-    <row r="36" ht="14.25" customHeight="1">
+      <c r="I35" s="4">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25" customHeight="1" spans="1:9">
       <c r="A36" s="2" t="s">
         <v>104</v>
       </c>
@@ -2948,16 +3816,16 @@
         <v>13</v>
       </c>
       <c r="F36" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I36" s="2">
-        <v>97.0</v>
-      </c>
-    </row>
-    <row r="37" ht="14.25" customHeight="1">
+      <c r="I36" s="4">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37" ht="14.25" customHeight="1" spans="1:9">
       <c r="A37" s="2" t="s">
         <v>107</v>
       </c>
@@ -2974,16 +3842,16 @@
         <v>13</v>
       </c>
       <c r="F37" s="2">
-        <v>2500.0</v>
+        <v>2500</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I37" s="2">
-        <v>487.0</v>
-      </c>
-    </row>
-    <row r="38" ht="14.25" customHeight="1">
+      <c r="I37" s="4">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="38" ht="14.25" customHeight="1" spans="1:9">
       <c r="A38" s="2" t="s">
         <v>107</v>
       </c>
@@ -3000,16 +3868,16 @@
         <v>13</v>
       </c>
       <c r="F38" s="2">
-        <v>2500.0</v>
+        <v>2500</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I38" s="2">
-        <v>487.0</v>
-      </c>
-    </row>
-    <row r="39" ht="14.25" customHeight="1">
+      <c r="I38" s="4">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="39" ht="14.25" customHeight="1" spans="1:9">
       <c r="A39" s="2" t="s">
         <v>111</v>
       </c>
@@ -3026,16 +3894,16 @@
         <v>13</v>
       </c>
       <c r="F39" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I39" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="40" ht="14.25" customHeight="1">
+      <c r="I39" s="4">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25" customHeight="1" spans="1:9">
       <c r="A40" s="2" t="s">
         <v>111</v>
       </c>
@@ -3052,16 +3920,16 @@
         <v>13</v>
       </c>
       <c r="F40" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I40" s="2">
-        <v>97.0</v>
-      </c>
-    </row>
-    <row r="41" ht="14.25" customHeight="1">
+      <c r="I40" s="4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="41" ht="14.25" customHeight="1" spans="1:9">
       <c r="A41" s="2" t="s">
         <v>116</v>
       </c>
@@ -3078,16 +3946,16 @@
         <v>13</v>
       </c>
       <c r="F41" s="2">
-        <v>1500.0</v>
+        <v>1500</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I41" s="2">
-        <v>292.0</v>
-      </c>
-    </row>
-    <row r="42" ht="14.25" customHeight="1">
+      <c r="I41" s="4">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="42" ht="14.25" customHeight="1" spans="1:9">
       <c r="A42" s="2" t="s">
         <v>118</v>
       </c>
@@ -3104,16 +3972,16 @@
         <v>13</v>
       </c>
       <c r="F42" s="2">
-        <v>7500.0</v>
+        <v>7500</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I42" s="2">
-        <v>1462.0</v>
-      </c>
-    </row>
-    <row r="43" ht="14.25" customHeight="1">
+      <c r="I42" s="4">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="43" ht="14.25" customHeight="1" spans="1:9">
       <c r="A43" s="2" t="s">
         <v>118</v>
       </c>
@@ -3130,16 +3998,16 @@
         <v>13</v>
       </c>
       <c r="F43" s="2">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I43" s="2">
-        <v>585.0</v>
-      </c>
-    </row>
-    <row r="44" ht="14.25" customHeight="1">
+      <c r="I43" s="4">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="44" ht="14.25" customHeight="1" spans="1:9">
       <c r="A44" s="2" t="s">
         <v>120</v>
       </c>
@@ -3156,16 +4024,16 @@
         <v>13</v>
       </c>
       <c r="F44" s="2">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I44" s="2">
-        <v>585.0</v>
-      </c>
-    </row>
-    <row r="45" ht="14.25" customHeight="1">
+      <c r="I44" s="4">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="45" ht="14.25" customHeight="1" spans="1:9">
       <c r="A45" s="2" t="s">
         <v>122</v>
       </c>
@@ -3182,16 +4050,16 @@
         <v>13</v>
       </c>
       <c r="F45" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I45" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="46" ht="14.25" customHeight="1">
+      <c r="I45" s="4">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="46" ht="14.25" customHeight="1" spans="1:9">
       <c r="A46" s="2" t="s">
         <v>125</v>
       </c>
@@ -3208,16 +4076,16 @@
         <v>13</v>
       </c>
       <c r="F46" s="2">
-        <v>35000.0</v>
+        <v>35000</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I46" s="2">
-        <v>6825.0</v>
-      </c>
-    </row>
-    <row r="47" ht="14.25" customHeight="1">
+      <c r="I46" s="4">
+        <v>6646</v>
+      </c>
+    </row>
+    <row r="47" ht="14.25" customHeight="1" spans="1:9">
       <c r="A47" s="2" t="s">
         <v>127</v>
       </c>
@@ -3234,16 +4102,16 @@
         <v>67</v>
       </c>
       <c r="F47" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I47" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="48" ht="14.25" customHeight="1">
+      <c r="I47" s="4">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="48" ht="14.25" customHeight="1" spans="1:9">
       <c r="A48" s="2" t="s">
         <v>131</v>
       </c>
@@ -3260,16 +4128,16 @@
         <v>13</v>
       </c>
       <c r="F48" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I48" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="49" ht="14.25" customHeight="1">
+      <c r="I48" s="4">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="49" ht="14.25" customHeight="1" spans="1:9">
       <c r="A49" s="2" t="s">
         <v>132</v>
       </c>
@@ -3286,16 +4154,16 @@
         <v>13</v>
       </c>
       <c r="F49" s="2">
-        <v>15000.0</v>
+        <v>15000</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I49" s="2">
-        <v>2925.0</v>
-      </c>
-    </row>
-    <row r="50" ht="14.25" customHeight="1">
+      <c r="I49" s="4">
+        <v>2876</v>
+      </c>
+    </row>
+    <row r="50" ht="14.25" customHeight="1" spans="1:9">
       <c r="A50" s="2" t="s">
         <v>132</v>
       </c>
@@ -3312,16 +4180,16 @@
         <v>13</v>
       </c>
       <c r="F50" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I50" s="2">
-        <v>97.0</v>
-      </c>
-    </row>
-    <row r="51" ht="14.25" customHeight="1">
+      <c r="I50" s="4">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="51" ht="14.25" customHeight="1" spans="1:9">
       <c r="A51" s="2" t="s">
         <v>132</v>
       </c>
@@ -3338,16 +4206,16 @@
         <v>13</v>
       </c>
       <c r="F51" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I51" s="2">
-        <v>250.0</v>
-      </c>
-    </row>
-    <row r="52" ht="14.25" customHeight="1">
+      <c r="I51" s="4">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="52" ht="14.25" customHeight="1" spans="1:9">
       <c r="A52" s="2" t="s">
         <v>132</v>
       </c>
@@ -3364,16 +4232,16 @@
         <v>13</v>
       </c>
       <c r="F52" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I52" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="53" ht="14.25" customHeight="1">
+      <c r="I52" s="4">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="53" ht="14.25" customHeight="1" spans="1:9">
       <c r="A53" s="2" t="s">
         <v>132</v>
       </c>
@@ -3390,16 +4258,16 @@
         <v>13</v>
       </c>
       <c r="F53" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I53" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="54" ht="14.25" customHeight="1">
+      <c r="I53" s="4">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="54" ht="14.25" customHeight="1" spans="1:9">
       <c r="A54" s="2" t="s">
         <v>132</v>
       </c>
@@ -3412,20 +4280,20 @@
       <c r="D54" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E54" s="3" t="s">
+      <c r="E54" t="s">
         <v>143</v>
       </c>
       <c r="F54" s="2">
-        <v>1500.0</v>
+        <v>1500</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I54" s="2">
-        <v>292.0</v>
-      </c>
-    </row>
-    <row r="55" ht="14.25" customHeight="1">
+      <c r="I54" s="4">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="55" ht="14.25" customHeight="1" spans="1:9">
       <c r="A55" s="2" t="s">
         <v>132</v>
       </c>
@@ -3442,16 +4310,16 @@
         <v>13</v>
       </c>
       <c r="F55" s="2">
-        <v>2500.0</v>
+        <v>2500</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I55" s="2">
-        <v>487.0</v>
-      </c>
-    </row>
-    <row r="56" ht="14.25" customHeight="1">
+      <c r="I55" s="4">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="56" ht="14.25" customHeight="1" spans="1:9">
       <c r="A56" s="2" t="s">
         <v>146</v>
       </c>
@@ -3468,16 +4336,16 @@
         <v>13</v>
       </c>
       <c r="F56" s="2">
-        <v>4000.0</v>
+        <v>4000</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I56" s="2">
-        <v>780.0</v>
-      </c>
-    </row>
-    <row r="57" ht="14.25" customHeight="1">
+      <c r="I56" s="4">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="57" ht="14.25" customHeight="1" spans="1:9">
       <c r="A57" s="2" t="s">
         <v>146</v>
       </c>
@@ -3494,16 +4362,16 @@
         <v>23</v>
       </c>
       <c r="F57" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I57" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="58" ht="14.25" customHeight="1">
+      <c r="I57" s="4">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="58" ht="14.25" customHeight="1" spans="1:9">
       <c r="A58" s="2" t="s">
         <v>149</v>
       </c>
@@ -3520,16 +4388,16 @@
         <v>13</v>
       </c>
       <c r="F58" s="2">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I58" s="2">
-        <v>585.0</v>
-      </c>
-    </row>
-    <row r="59" ht="14.25" customHeight="1">
+      <c r="I58" s="4">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="59" ht="14.25" customHeight="1" spans="1:9">
       <c r="A59" s="2" t="s">
         <v>152</v>
       </c>
@@ -3546,16 +4414,16 @@
         <v>13</v>
       </c>
       <c r="F59" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I59" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="60" ht="14.25" customHeight="1">
+      <c r="I59" s="4">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="60" ht="14.25" customHeight="1" spans="1:9">
       <c r="A60" s="2" t="s">
         <v>152</v>
       </c>
@@ -3572,16 +4440,16 @@
         <v>13</v>
       </c>
       <c r="F60" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I60" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="61" ht="14.25" customHeight="1">
+      <c r="I60" s="4">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="61" ht="14.25" customHeight="1" spans="1:9">
       <c r="A61" s="2" t="s">
         <v>155</v>
       </c>
@@ -3598,16 +4466,16 @@
         <v>40</v>
       </c>
       <c r="F61" s="2">
-        <v>17000.0</v>
+        <v>17000</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I61" s="2">
-        <v>3315.0</v>
-      </c>
-    </row>
-    <row r="62" ht="14.25" customHeight="1">
+      <c r="I61" s="4">
+        <v>3388</v>
+      </c>
+    </row>
+    <row r="62" ht="14.25" customHeight="1" spans="1:9">
       <c r="A62" s="2" t="s">
         <v>157</v>
       </c>
@@ -3624,16 +4492,16 @@
         <v>13</v>
       </c>
       <c r="F62" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I62" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="63" ht="14.25" customHeight="1">
+      <c r="I62" s="4">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="63" ht="14.25" customHeight="1" spans="1:9">
       <c r="A63" s="2" t="s">
         <v>157</v>
       </c>
@@ -3650,16 +4518,16 @@
         <v>13</v>
       </c>
       <c r="F63" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I63" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="64" ht="14.25" customHeight="1">
+      <c r="I63" s="4">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="64" ht="14.25" customHeight="1" spans="1:9">
       <c r="A64" s="2" t="s">
         <v>160</v>
       </c>
@@ -3676,16 +4544,16 @@
         <v>13</v>
       </c>
       <c r="F64" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I64" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="65" ht="14.25" customHeight="1">
+      <c r="I64" s="4">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="65" ht="14.25" customHeight="1" spans="1:9">
       <c r="A65" s="2" t="s">
         <v>161</v>
       </c>
@@ -3702,16 +4570,16 @@
         <v>13</v>
       </c>
       <c r="F65" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I65" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="66" ht="14.25" customHeight="1">
+      <c r="I65" s="4">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="66" ht="14.25" customHeight="1" spans="1:9">
       <c r="A66" s="2" t="s">
         <v>162</v>
       </c>
@@ -3728,16 +4596,16 @@
         <v>13</v>
       </c>
       <c r="F66" s="2">
-        <v>15000.0</v>
+        <v>15000</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I66" s="2">
-        <v>2925.0</v>
-      </c>
-    </row>
-    <row r="67" ht="14.25" customHeight="1">
+      <c r="I66" s="4">
+        <v>2917</v>
+      </c>
+    </row>
+    <row r="67" ht="14.25" customHeight="1" spans="1:9">
       <c r="A67" s="2" t="s">
         <v>164</v>
       </c>
@@ -3754,16 +4622,16 @@
         <v>13</v>
       </c>
       <c r="F67" s="2">
-        <v>6000.0</v>
+        <v>6000</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I67" s="2">
-        <v>1170.0</v>
-      </c>
-    </row>
-    <row r="68" ht="14.25" customHeight="1">
+      <c r="I67" s="4">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="68" ht="14.25" customHeight="1" spans="1:9">
       <c r="A68" s="2" t="s">
         <v>164</v>
       </c>
@@ -3780,16 +4648,16 @@
         <v>13</v>
       </c>
       <c r="F68" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I68" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="69" ht="14.25" customHeight="1">
+      <c r="I68" s="4">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="69" ht="14.25" customHeight="1" spans="1:9">
       <c r="A69" s="2" t="s">
         <v>164</v>
       </c>
@@ -3806,16 +4674,16 @@
         <v>13</v>
       </c>
       <c r="F69" s="2">
-        <v>4500.0</v>
+        <v>4500</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I69" s="2">
-        <v>877.0</v>
-      </c>
-    </row>
-    <row r="70" ht="14.25" customHeight="1">
+      <c r="I69" s="4">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="70" ht="14.25" customHeight="1" spans="1:9">
       <c r="A70" s="2" t="s">
         <v>164</v>
       </c>
@@ -3832,16 +4700,16 @@
         <v>13</v>
       </c>
       <c r="F70" s="2">
-        <v>6000.0</v>
+        <v>6000</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I70" s="2">
-        <v>1170.0</v>
-      </c>
-    </row>
-    <row r="71" ht="14.25" customHeight="1">
+      <c r="I70" s="4">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="71" ht="14.25" customHeight="1" spans="1:9">
       <c r="A71" s="2" t="s">
         <v>169</v>
       </c>
@@ -3858,16 +4726,16 @@
         <v>13</v>
       </c>
       <c r="F71" s="2">
-        <v>5500.0</v>
+        <v>5500</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I71" s="2">
-        <v>1072.0</v>
-      </c>
-    </row>
-    <row r="72" ht="14.25" customHeight="1">
+      <c r="I71" s="4">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="72" ht="14.25" customHeight="1" spans="1:9">
       <c r="A72" s="2" t="s">
         <v>169</v>
       </c>
@@ -3884,23 +4752,23 @@
         <v>13</v>
       </c>
       <c r="F72" s="2">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I72" s="2">
-        <v>585.0</v>
-      </c>
-    </row>
-    <row r="73" ht="14.25" customHeight="1">
+      <c r="I72" s="4">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="73" ht="14.25" customHeight="1" spans="1:9">
       <c r="A73" s="2" t="s">
         <v>172</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C73" t="s">
         <v>174</v>
       </c>
       <c r="D73" s="2" t="s">
@@ -3910,16 +4778,16 @@
         <v>23</v>
       </c>
       <c r="F73" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I73" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="74" ht="14.25" customHeight="1">
+      <c r="I73" s="4">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="74" ht="14.25" customHeight="1" spans="1:9">
       <c r="A74" s="2" t="s">
         <v>172</v>
       </c>
@@ -3936,16 +4804,16 @@
         <v>13</v>
       </c>
       <c r="F74" s="2">
-        <v>20000.0</v>
+        <v>20000</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I74" s="2">
-        <v>3900.0</v>
-      </c>
-    </row>
-    <row r="75" ht="14.25" customHeight="1">
+      <c r="I74" s="4">
+        <v>3861</v>
+      </c>
+    </row>
+    <row r="75" ht="14.25" customHeight="1" spans="1:9">
       <c r="A75" s="2" t="s">
         <v>177</v>
       </c>
@@ -3962,20 +4830,20 @@
         <v>13</v>
       </c>
       <c r="F75" s="2">
-        <v>15000.0</v>
+        <v>15000</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I75" s="2">
-        <v>2925.0</v>
-      </c>
-    </row>
-    <row r="76" ht="14.25" customHeight="1">
+      <c r="I75" s="4">
+        <v>2967</v>
+      </c>
+    </row>
+    <row r="76" ht="14.25" customHeight="1" spans="1:9">
       <c r="A76" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" t="s">
         <v>180</v>
       </c>
       <c r="C76" s="2" t="s">
@@ -3988,16 +4856,16 @@
         <v>13</v>
       </c>
       <c r="F76" s="2">
-        <v>30000.0</v>
+        <v>30000</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I76" s="2">
-        <v>5850.0</v>
-      </c>
-    </row>
-    <row r="77" ht="14.25" customHeight="1">
+      <c r="I76" s="4">
+        <v>5856</v>
+      </c>
+    </row>
+    <row r="77" ht="14.25" customHeight="1" spans="1:9">
       <c r="A77" s="2" t="s">
         <v>179</v>
       </c>
@@ -4014,16 +4882,16 @@
         <v>40</v>
       </c>
       <c r="F77" s="2">
-        <v>20000.0</v>
+        <v>20000</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I77" s="2">
-        <v>3900.0</v>
-      </c>
-    </row>
-    <row r="78" ht="14.25" customHeight="1">
+      <c r="I77" s="4">
+        <v>3822</v>
+      </c>
+    </row>
+    <row r="78" ht="14.25" customHeight="1" spans="1:9">
       <c r="A78" s="2" t="s">
         <v>179</v>
       </c>
@@ -4040,16 +4908,16 @@
         <v>13</v>
       </c>
       <c r="F78" s="2">
-        <v>30000.0</v>
+        <v>30000</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I78" s="2">
-        <v>5850.0</v>
-      </c>
-    </row>
-    <row r="79" ht="14.25" customHeight="1">
+      <c r="I78" s="4">
+        <v>5748</v>
+      </c>
+    </row>
+    <row r="79" ht="14.25" customHeight="1" spans="1:9">
       <c r="A79" s="2" t="s">
         <v>188</v>
       </c>
@@ -4066,16 +4934,16 @@
         <v>13</v>
       </c>
       <c r="F79" s="2">
-        <v>12000.0</v>
+        <v>12000</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I79" s="2">
-        <v>2340.0</v>
-      </c>
-    </row>
-    <row r="80" ht="14.25" customHeight="1">
+      <c r="I79" s="4">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="80" ht="14.25" customHeight="1" spans="1:9">
       <c r="A80" s="2" t="s">
         <v>192</v>
       </c>
@@ -4092,16 +4960,16 @@
         <v>13</v>
       </c>
       <c r="F80" s="2">
-        <v>30000.0</v>
+        <v>30000</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I80" s="2">
-        <v>5850.0</v>
-      </c>
-    </row>
-    <row r="81" ht="14.25" customHeight="1">
+      <c r="I80" s="4">
+        <v>5912</v>
+      </c>
+    </row>
+    <row r="81" ht="14.25" customHeight="1" spans="1:9">
       <c r="A81" s="2" t="s">
         <v>195</v>
       </c>
@@ -4118,16 +4986,16 @@
         <v>13</v>
       </c>
       <c r="F81" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I81" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="82" ht="14.25" customHeight="1">
+      <c r="I81" s="4">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="82" ht="14.25" customHeight="1" spans="1:9">
       <c r="A82" s="2" t="s">
         <v>197</v>
       </c>
@@ -4144,23 +5012,23 @@
         <v>13</v>
       </c>
       <c r="F82" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I82" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="83" ht="14.25" customHeight="1">
+      <c r="I82" s="4">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="83" ht="14.25" customHeight="1" spans="1:9">
       <c r="A83" s="2" t="s">
         <v>197</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C83" t="s">
         <v>106</v>
       </c>
       <c r="D83" s="2" t="s">
@@ -4170,16 +5038,16 @@
         <v>13</v>
       </c>
       <c r="F83" s="2">
-        <v>15000.0</v>
+        <v>15000</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I83" s="2">
-        <v>2925.0</v>
-      </c>
-    </row>
-    <row r="84" ht="14.25" customHeight="1">
+      <c r="I83" s="4">
+        <v>2993</v>
+      </c>
+    </row>
+    <row r="84" ht="14.25" customHeight="1" spans="1:9">
       <c r="A84" s="2" t="s">
         <v>197</v>
       </c>
@@ -4196,16 +5064,16 @@
         <v>13</v>
       </c>
       <c r="F84" s="2">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I84" s="2">
-        <v>585.0</v>
-      </c>
-    </row>
-    <row r="85" ht="14.25" customHeight="1">
+      <c r="I84" s="4">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="85" ht="14.25" customHeight="1" spans="1:9">
       <c r="A85" s="2" t="s">
         <v>197</v>
       </c>
@@ -4222,16 +5090,16 @@
         <v>13</v>
       </c>
       <c r="F85" s="2">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I85" s="2">
-        <v>585.0</v>
-      </c>
-    </row>
-    <row r="86" ht="14.25" customHeight="1">
+      <c r="I85" s="4">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="86" ht="14.25" customHeight="1" spans="1:9">
       <c r="A86" s="2" t="s">
         <v>202</v>
       </c>
@@ -4248,23 +5116,23 @@
         <v>13</v>
       </c>
       <c r="F86" s="2">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I86" s="2">
-        <v>585.0</v>
-      </c>
-    </row>
-    <row r="87" ht="14.25" customHeight="1">
+      <c r="I86" s="4">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="87" ht="14.25" customHeight="1" spans="1:9">
       <c r="A87" s="2" t="s">
         <v>202</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C87" t="s">
         <v>134</v>
       </c>
       <c r="D87" s="2" t="s">
@@ -4274,16 +5142,16 @@
         <v>13</v>
       </c>
       <c r="F87" s="2">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I87" s="2">
-        <v>585.0</v>
-      </c>
-    </row>
-    <row r="88" ht="14.25" customHeight="1">
+      <c r="I87" s="4">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="88" ht="14.25" customHeight="1" spans="1:9">
       <c r="A88" s="2" t="s">
         <v>205</v>
       </c>
@@ -4300,23 +5168,23 @@
         <v>13</v>
       </c>
       <c r="F88" s="2">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I88" s="2">
-        <v>37.0</v>
-      </c>
-    </row>
-    <row r="89" ht="14.25" customHeight="1">
+      <c r="I88" s="4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="89" ht="14.25" customHeight="1" spans="1:9">
       <c r="A89" s="2" t="s">
         <v>205</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="C89" t="s">
         <v>106</v>
       </c>
       <c r="D89" s="2" t="s">
@@ -4326,16 +5194,16 @@
         <v>13</v>
       </c>
       <c r="F89" s="2">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I89" s="2">
-        <v>585.0</v>
-      </c>
-    </row>
-    <row r="90" ht="14.25" customHeight="1">
+      <c r="I89" s="4">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="90" ht="14.25" customHeight="1" spans="1:9">
       <c r="A90" s="2" t="s">
         <v>207</v>
       </c>
@@ -4352,16 +5220,16 @@
         <v>13</v>
       </c>
       <c r="F90" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I90" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="91" ht="14.25" customHeight="1">
+      <c r="I90" s="4">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="91" ht="14.25" customHeight="1" spans="1:9">
       <c r="A91" s="2" t="s">
         <v>209</v>
       </c>
@@ -4378,16 +5246,16 @@
         <v>13</v>
       </c>
       <c r="F91" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I91" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="92" ht="14.25" customHeight="1">
+      <c r="I91" s="4">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="92" ht="14.25" customHeight="1" spans="1:9">
       <c r="A92" s="2" t="s">
         <v>209</v>
       </c>
@@ -4404,16 +5272,16 @@
         <v>13</v>
       </c>
       <c r="F92" s="2">
-        <v>8000.0</v>
+        <v>8000</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I92" s="2">
-        <v>1560.0</v>
-      </c>
-    </row>
-    <row r="93" ht="14.25" customHeight="1">
+      <c r="I92" s="4">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="93" ht="14.25" customHeight="1" spans="1:9">
       <c r="A93" s="2" t="s">
         <v>209</v>
       </c>
@@ -4430,16 +5298,16 @@
         <v>13</v>
       </c>
       <c r="F93" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I93" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="94" ht="14.25" customHeight="1">
+      <c r="I93" s="4">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="94" ht="14.25" customHeight="1" spans="1:9">
       <c r="A94" s="2" t="s">
         <v>213</v>
       </c>
@@ -4456,16 +5324,16 @@
         <v>13</v>
       </c>
       <c r="F94" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I94" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="95" ht="14.25" customHeight="1">
+      <c r="I94" s="4">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="95" ht="14.25" customHeight="1" spans="1:9">
       <c r="A95" s="2" t="s">
         <v>215</v>
       </c>
@@ -4482,16 +5350,16 @@
         <v>13</v>
       </c>
       <c r="F95" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I95" s="2">
-        <v>159.0</v>
-      </c>
-    </row>
-    <row r="96" ht="14.25" customHeight="1">
+      <c r="I95" s="4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" ht="14.25" customHeight="1" spans="1:9">
       <c r="A96" s="2" t="s">
         <v>217</v>
       </c>
@@ -4508,16 +5376,16 @@
         <v>13</v>
       </c>
       <c r="F96" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I96" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="97" ht="14.25" customHeight="1">
+      <c r="I96" s="4">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="97" ht="14.25" customHeight="1" spans="1:9">
       <c r="A97" s="2" t="s">
         <v>219</v>
       </c>
@@ -4534,16 +5402,16 @@
         <v>13</v>
       </c>
       <c r="F97" s="2">
-        <v>50000.0</v>
+        <v>50000</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I97" s="2">
-        <v>9750.0</v>
-      </c>
-    </row>
-    <row r="98" ht="14.25" customHeight="1">
+      <c r="I97" s="4">
+        <v>9992</v>
+      </c>
+    </row>
+    <row r="98" ht="14.25" customHeight="1" spans="1:9">
       <c r="A98" s="2" t="s">
         <v>221</v>
       </c>
@@ -4560,16 +5428,16 @@
         <v>13</v>
       </c>
       <c r="F98" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I98" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="99" ht="14.25" customHeight="1">
+      <c r="I98" s="4">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="99" ht="14.25" customHeight="1" spans="1:9">
       <c r="A99" s="2" t="s">
         <v>221</v>
       </c>
@@ -4586,16 +5454,16 @@
         <v>13</v>
       </c>
       <c r="F99" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I99" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="100" ht="14.25" customHeight="1">
+      <c r="I99" s="4">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="100" ht="14.25" customHeight="1" spans="1:9">
       <c r="A100" s="2" t="s">
         <v>225</v>
       </c>
@@ -4612,16 +5480,16 @@
         <v>13</v>
       </c>
       <c r="F100" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I100" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="101" ht="14.25" customHeight="1">
+      <c r="I100" s="4">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="101" ht="14.25" customHeight="1" spans="1:9">
       <c r="A101" s="2" t="s">
         <v>227</v>
       </c>
@@ -4638,16 +5506,16 @@
         <v>13</v>
       </c>
       <c r="F101" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I101" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="102" ht="14.25" customHeight="1">
+      <c r="I101" s="4">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="102" ht="14.25" customHeight="1" spans="1:9">
       <c r="A102" s="2" t="s">
         <v>229</v>
       </c>
@@ -4664,16 +5532,16 @@
         <v>13</v>
       </c>
       <c r="F102" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I102" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="103" ht="14.25" customHeight="1">
+      <c r="I102" s="4">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="103" ht="14.25" customHeight="1" spans="1:9">
       <c r="A103" s="2" t="s">
         <v>229</v>
       </c>
@@ -4690,16 +5558,16 @@
         <v>13</v>
       </c>
       <c r="F103" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I103" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="104" ht="14.25" customHeight="1">
+      <c r="I103" s="4">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="104" ht="14.25" customHeight="1" spans="1:9">
       <c r="A104" s="2" t="s">
         <v>229</v>
       </c>
@@ -4716,16 +5584,16 @@
         <v>67</v>
       </c>
       <c r="F104" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I104" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="105" ht="14.25" customHeight="1">
+      <c r="I104" s="4">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="105" ht="14.25" customHeight="1" spans="1:9">
       <c r="A105" s="2" t="s">
         <v>229</v>
       </c>
@@ -4742,16 +5610,16 @@
         <v>13</v>
       </c>
       <c r="F105" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I105" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="106" ht="14.25" customHeight="1">
+      <c r="I105" s="4">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="106" ht="14.25" customHeight="1" spans="1:9">
       <c r="A106" s="2" t="s">
         <v>229</v>
       </c>
@@ -4768,16 +5636,16 @@
         <v>13</v>
       </c>
       <c r="F106" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I106" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="107" ht="14.25" customHeight="1">
+      <c r="I106" s="4">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="107" ht="14.25" customHeight="1" spans="1:9">
       <c r="A107" s="2" t="s">
         <v>229</v>
       </c>
@@ -4794,16 +5662,16 @@
         <v>13</v>
       </c>
       <c r="F107" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I107" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="108" ht="14.25" customHeight="1">
+      <c r="I107" s="4">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="108" ht="14.25" customHeight="1" spans="1:9">
       <c r="A108" s="2" t="s">
         <v>229</v>
       </c>
@@ -4820,16 +5688,16 @@
         <v>13</v>
       </c>
       <c r="F108" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I108" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="109" ht="14.25" customHeight="1">
+      <c r="I108" s="4">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="109" ht="14.25" customHeight="1" spans="1:9">
       <c r="A109" s="2" t="s">
         <v>229</v>
       </c>
@@ -4846,16 +5714,16 @@
         <v>40</v>
       </c>
       <c r="F109" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I109" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="110" ht="14.25" customHeight="1">
+      <c r="I109" s="4">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="110" ht="14.25" customHeight="1" spans="1:9">
       <c r="A110" s="2" t="s">
         <v>243</v>
       </c>
@@ -4872,16 +5740,16 @@
         <v>23</v>
       </c>
       <c r="F110" s="2">
-        <v>80000.0</v>
+        <v>80000</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I110" s="2">
-        <v>15600.0</v>
-      </c>
-    </row>
-    <row r="111" ht="14.25" customHeight="1">
+      <c r="I110" s="4">
+        <v>15872</v>
+      </c>
+    </row>
+    <row r="111" ht="14.25" customHeight="1" spans="1:9">
       <c r="A111" s="2" t="s">
         <v>247</v>
       </c>
@@ -4898,16 +5766,16 @@
         <v>13</v>
       </c>
       <c r="F111" s="2">
-        <v>5750.0</v>
+        <v>5750</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I111" s="2">
-        <v>1121.0</v>
-      </c>
-    </row>
-    <row r="112" ht="14.25" customHeight="1">
+      <c r="I111" s="4">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="112" ht="14.25" customHeight="1" spans="1:9">
       <c r="A112" s="2" t="s">
         <v>249</v>
       </c>
@@ -4924,16 +5792,16 @@
         <v>13</v>
       </c>
       <c r="F112" s="2">
-        <v>3500.0</v>
+        <v>3500</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I112" s="2">
-        <v>682.0</v>
-      </c>
-    </row>
-    <row r="113" ht="14.25" customHeight="1">
+      <c r="I112" s="4">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="113" ht="14.25" customHeight="1" spans="1:9">
       <c r="A113" s="2" t="s">
         <v>251</v>
       </c>
@@ -4950,16 +5818,16 @@
         <v>13</v>
       </c>
       <c r="F113" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I113" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="114" ht="14.25" customHeight="1">
+      <c r="I113" s="4">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="114" ht="14.25" customHeight="1" spans="1:9">
       <c r="A114" s="2" t="s">
         <v>251</v>
       </c>
@@ -4976,16 +5844,16 @@
         <v>13</v>
       </c>
       <c r="F114" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I114" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="115" ht="14.25" customHeight="1">
+      <c r="I114" s="4">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="115" ht="14.25" customHeight="1" spans="1:9">
       <c r="A115" s="2" t="s">
         <v>251</v>
       </c>
@@ -5002,16 +5870,16 @@
         <v>13</v>
       </c>
       <c r="F115" s="2">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I115" s="2">
-        <v>585.0</v>
-      </c>
-    </row>
-    <row r="116" ht="14.25" customHeight="1">
+      <c r="I115" s="4">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="116" ht="14.25" customHeight="1" spans="1:9">
       <c r="A116" s="2" t="s">
         <v>256</v>
       </c>
@@ -5028,16 +5896,16 @@
         <v>13</v>
       </c>
       <c r="F116" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I116" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="117" ht="14.25" customHeight="1">
+      <c r="I116" s="4">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="117" ht="14.25" customHeight="1" spans="1:9">
       <c r="A117" s="2" t="s">
         <v>259</v>
       </c>
@@ -5054,16 +5922,16 @@
         <v>13</v>
       </c>
       <c r="F117" s="2">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I117" s="2">
-        <v>58.0</v>
-      </c>
-    </row>
-    <row r="118" ht="14.25" customHeight="1">
+      <c r="I117" s="4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="118" ht="14.25" customHeight="1" spans="1:9">
       <c r="A118" s="2" t="s">
         <v>259</v>
       </c>
@@ -5080,16 +5948,16 @@
         <v>23</v>
       </c>
       <c r="F118" s="2">
-        <v>4000.0</v>
+        <v>4000</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I118" s="2">
-        <v>780.0</v>
-      </c>
-    </row>
-    <row r="119" ht="14.25" customHeight="1">
+      <c r="I118" s="4">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="119" ht="14.25" customHeight="1" spans="1:9">
       <c r="A119" s="2" t="s">
         <v>263</v>
       </c>
@@ -5106,16 +5974,16 @@
         <v>13</v>
       </c>
       <c r="F119" s="2">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I119" s="2">
-        <v>585.0</v>
-      </c>
-    </row>
-    <row r="120" ht="14.25" customHeight="1">
+      <c r="I119" s="4">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="120" ht="14.25" customHeight="1" spans="1:9">
       <c r="A120" s="2" t="s">
         <v>263</v>
       </c>
@@ -5132,23 +6000,23 @@
         <v>13</v>
       </c>
       <c r="F120" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I120" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="121" ht="14.25" customHeight="1">
+      <c r="I120" s="4">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="121" ht="14.25" customHeight="1" spans="1:9">
       <c r="A121" s="2" t="s">
         <v>263</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="C121" t="s">
         <v>75</v>
       </c>
       <c r="D121" s="2" t="s">
@@ -5158,16 +6026,16 @@
         <v>13</v>
       </c>
       <c r="F121" s="2">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I121" s="2">
-        <v>585.0</v>
-      </c>
-    </row>
-    <row r="122" ht="14.25" customHeight="1">
+      <c r="I121" s="4">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="122" ht="14.25" customHeight="1" spans="1:9">
       <c r="A122" s="2" t="s">
         <v>263</v>
       </c>
@@ -5184,16 +6052,16 @@
         <v>13</v>
       </c>
       <c r="F122" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I122" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="123" ht="14.25" customHeight="1">
+      <c r="I122" s="4">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="123" ht="14.25" customHeight="1" spans="1:9">
       <c r="A123" s="2" t="s">
         <v>263</v>
       </c>
@@ -5210,16 +6078,16 @@
         <v>13</v>
       </c>
       <c r="F123" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I123" s="2">
-        <v>97.0</v>
-      </c>
-    </row>
-    <row r="124" ht="14.25" customHeight="1">
+      <c r="I123" s="4">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="124" ht="14.25" customHeight="1" spans="1:9">
       <c r="A124" s="2" t="s">
         <v>263</v>
       </c>
@@ -5236,16 +6104,16 @@
         <v>13</v>
       </c>
       <c r="F124" s="2">
-        <v>40000.0</v>
+        <v>40000</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I124" s="2">
-        <v>7800.0</v>
-      </c>
-    </row>
-    <row r="125" ht="14.25" customHeight="1">
+      <c r="I124" s="4">
+        <v>7535</v>
+      </c>
+    </row>
+    <row r="125" ht="14.25" customHeight="1" spans="1:9">
       <c r="A125" s="2" t="s">
         <v>270</v>
       </c>
@@ -5262,16 +6130,16 @@
         <v>13</v>
       </c>
       <c r="F125" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I125" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="126" ht="14.25" customHeight="1">
+      <c r="I125" s="4">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="126" ht="14.25" customHeight="1" spans="1:9">
       <c r="A126" s="2" t="s">
         <v>270</v>
       </c>
@@ -5288,16 +6156,16 @@
         <v>13</v>
       </c>
       <c r="F126" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I126" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="127" ht="14.25" customHeight="1">
+      <c r="I126" s="4">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="127" ht="14.25" customHeight="1" spans="1:9">
       <c r="A127" s="2" t="s">
         <v>270</v>
       </c>
@@ -5314,16 +6182,16 @@
         <v>13</v>
       </c>
       <c r="F127" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I127" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="128" ht="14.25" customHeight="1">
+      <c r="I127" s="4">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="128" ht="14.25" customHeight="1" spans="1:9">
       <c r="A128" s="2" t="s">
         <v>275</v>
       </c>
@@ -5340,16 +6208,16 @@
         <v>13</v>
       </c>
       <c r="F128" s="2">
-        <v>15000.0</v>
+        <v>15000</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I128" s="2">
-        <v>2925.0</v>
-      </c>
-    </row>
-    <row r="129" ht="14.25" customHeight="1">
+      <c r="I128" s="4">
+        <v>2829</v>
+      </c>
+    </row>
+    <row r="129" ht="14.25" customHeight="1" spans="1:9">
       <c r="A129" s="2" t="s">
         <v>276</v>
       </c>
@@ -5366,16 +6234,16 @@
         <v>13</v>
       </c>
       <c r="F129" s="2">
-        <v>150.0</v>
+        <v>150</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I129" s="2">
-        <v>39.0</v>
-      </c>
-    </row>
-    <row r="130" ht="14.25" customHeight="1">
+      <c r="I129" s="4">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="130" ht="14.25" customHeight="1" spans="1:9">
       <c r="A130" s="2" t="s">
         <v>278</v>
       </c>
@@ -5392,16 +6260,16 @@
         <v>13</v>
       </c>
       <c r="F130" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I130" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="131" ht="14.25" customHeight="1">
+      <c r="I130" s="4">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="131" ht="14.25" customHeight="1" spans="1:9">
       <c r="A131" s="2" t="s">
         <v>278</v>
       </c>
@@ -5418,16 +6286,16 @@
         <v>13</v>
       </c>
       <c r="F131" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I131" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="132" ht="14.25" customHeight="1">
+      <c r="I131" s="4">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="132" ht="14.25" customHeight="1" spans="1:9">
       <c r="A132" s="2" t="s">
         <v>278</v>
       </c>
@@ -5444,16 +6312,16 @@
         <v>13</v>
       </c>
       <c r="F132" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I132" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="133" ht="14.25" customHeight="1">
+      <c r="I132" s="4">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="133" ht="14.25" customHeight="1" spans="1:9">
       <c r="A133" s="2" t="s">
         <v>283</v>
       </c>
@@ -5470,16 +6338,16 @@
         <v>13</v>
       </c>
       <c r="F133" s="2">
-        <v>20000.0</v>
+        <v>20000</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I133" s="2">
-        <v>3900.0</v>
-      </c>
-    </row>
-    <row r="134" ht="14.25" customHeight="1">
+      <c r="I133" s="4">
+        <v>3859</v>
+      </c>
+    </row>
+    <row r="134" ht="14.25" customHeight="1" spans="1:9">
       <c r="A134" s="2" t="s">
         <v>283</v>
       </c>
@@ -5496,16 +6364,16 @@
         <v>13</v>
       </c>
       <c r="F134" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I134" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="135" ht="14.25" customHeight="1">
+      <c r="I134" s="4">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="135" ht="14.25" customHeight="1" spans="1:9">
       <c r="A135" s="2" t="s">
         <v>287</v>
       </c>
@@ -5522,16 +6390,16 @@
         <v>13</v>
       </c>
       <c r="F135" s="2">
-        <v>25000.0</v>
+        <v>25000</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I135" s="2">
-        <v>4875.0</v>
-      </c>
-    </row>
-    <row r="136" ht="14.25" customHeight="1">
+      <c r="I135" s="4">
+        <v>4768</v>
+      </c>
+    </row>
+    <row r="136" ht="14.25" customHeight="1" spans="1:9">
       <c r="A136" s="2" t="s">
         <v>290</v>
       </c>
@@ -5548,16 +6416,16 @@
         <v>13</v>
       </c>
       <c r="F136" s="2">
-        <v>4400.0</v>
+        <v>4400</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I136" s="2">
-        <v>858.0</v>
-      </c>
-    </row>
-    <row r="137" ht="14.25" customHeight="1">
+      <c r="I136" s="4">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="137" ht="14.25" customHeight="1" spans="1:9">
       <c r="A137" s="2" t="s">
         <v>293</v>
       </c>
@@ -5574,16 +6442,16 @@
         <v>13</v>
       </c>
       <c r="F137" s="2">
-        <v>20000.0</v>
+        <v>20000</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I137" s="2">
-        <v>3900.0</v>
-      </c>
-    </row>
-    <row r="138" ht="14.25" customHeight="1">
+      <c r="I137" s="4">
+        <v>3973</v>
+      </c>
+    </row>
+    <row r="138" ht="14.25" customHeight="1" spans="1:9">
       <c r="A138" s="2" t="s">
         <v>294</v>
       </c>
@@ -5600,42 +6468,42 @@
         <v>23</v>
       </c>
       <c r="F138" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I138" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="139" ht="14.25" customHeight="1">
+      <c r="I138" s="4">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="139" ht="14.25" customHeight="1" spans="1:9">
       <c r="A139" s="2" t="s">
         <v>297</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="C139" s="3" t="s">
+      <c r="C139" t="s">
         <v>212</v>
       </c>
-      <c r="D139" s="3" t="s">
+      <c r="D139" t="s">
         <v>18</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F139" s="2">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I139" s="2">
-        <v>585.0</v>
-      </c>
-    </row>
-    <row r="140" ht="14.25" customHeight="1">
+      <c r="I139" s="4">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="140" ht="14.25" customHeight="1" spans="1:9">
       <c r="A140" s="2" t="s">
         <v>299</v>
       </c>
@@ -5648,20 +6516,20 @@
       <c r="D140" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="E140" s="3" t="s">
+      <c r="E140" t="s">
         <v>40</v>
       </c>
       <c r="F140" s="2">
-        <v>1500.0</v>
+        <v>1500</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I140" s="2">
-        <v>292.0</v>
-      </c>
-    </row>
-    <row r="141" ht="14.25" customHeight="1">
+      <c r="I140" s="4">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="141" ht="14.25" customHeight="1" spans="1:9">
       <c r="A141" s="2" t="s">
         <v>299</v>
       </c>
@@ -5671,23 +6539,23 @@
       <c r="C141" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="D141" s="3" t="s">
+      <c r="D141" t="s">
         <v>305</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>143</v>
       </c>
       <c r="F141" s="2">
-        <v>1500.0</v>
+        <v>1500</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I141" s="2">
-        <v>292.0</v>
-      </c>
-    </row>
-    <row r="142" ht="14.25" customHeight="1">
+      <c r="I141" s="4">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="142" ht="14.25" customHeight="1" spans="1:9">
       <c r="A142" s="2" t="s">
         <v>299</v>
       </c>
@@ -5704,16 +6572,16 @@
         <v>13</v>
       </c>
       <c r="F142" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I142" s="2">
-        <v>279.0</v>
-      </c>
-    </row>
-    <row r="143" ht="14.25" customHeight="1">
+      <c r="I142" s="4">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="143" ht="14.25" customHeight="1" spans="1:9">
       <c r="A143" s="2" t="s">
         <v>307</v>
       </c>
@@ -5730,16 +6598,16 @@
         <v>311</v>
       </c>
       <c r="F143" s="2">
-        <v>30000.0</v>
+        <v>30000</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I143" s="2">
-        <v>5850.0</v>
-      </c>
-    </row>
-    <row r="144" ht="14.25" customHeight="1">
+      <c r="I143" s="4">
+        <v>5981</v>
+      </c>
+    </row>
+    <row r="144" ht="14.25" customHeight="1" spans="1:9">
       <c r="A144" s="2" t="s">
         <v>312</v>
       </c>
@@ -5756,16 +6624,16 @@
         <v>311</v>
       </c>
       <c r="F144" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I144" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="145" ht="14.25" customHeight="1">
+      <c r="I144" s="4">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="145" ht="14.25" customHeight="1" spans="1:9">
       <c r="A145" s="2" t="s">
         <v>315</v>
       </c>
@@ -5782,16 +6650,16 @@
         <v>13</v>
       </c>
       <c r="F145" s="2">
-        <v>10000.0</v>
+        <v>10000</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I145" s="2">
-        <v>1950.0</v>
-      </c>
-    </row>
-    <row r="146" ht="14.25" customHeight="1">
+      <c r="I145" s="4">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="146" ht="14.25" customHeight="1" spans="1:9">
       <c r="A146" s="2" t="s">
         <v>318</v>
       </c>
@@ -5808,16 +6676,16 @@
         <v>13</v>
       </c>
       <c r="F146" s="2">
-        <v>10000.0</v>
+        <v>10000</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I146" s="2">
-        <v>1950.0</v>
-      </c>
-    </row>
-    <row r="147" ht="14.25" customHeight="1">
+      <c r="I146" s="4">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="147" ht="14.25" customHeight="1" spans="1:9">
       <c r="A147" s="2" t="s">
         <v>318</v>
       </c>
@@ -5834,16 +6702,16 @@
         <v>13</v>
       </c>
       <c r="F147" s="2">
-        <v>5700.0</v>
+        <v>5700</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I147" s="2">
-        <v>1111.0</v>
-      </c>
-    </row>
-    <row r="148" ht="14.25" customHeight="1">
+      <c r="I147" s="4">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="148" ht="14.25" customHeight="1" spans="1:9">
       <c r="A148" s="2" t="s">
         <v>318</v>
       </c>
@@ -5860,16 +6728,16 @@
         <v>13</v>
       </c>
       <c r="F148" s="2">
-        <v>1500.0</v>
+        <v>1500</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I148" s="2">
-        <v>292.0</v>
-      </c>
-    </row>
-    <row r="149" ht="14.25" customHeight="1">
+      <c r="I148" s="4">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="149" ht="14.25" customHeight="1" spans="1:9">
       <c r="A149" s="2" t="s">
         <v>318</v>
       </c>
@@ -5886,16 +6754,16 @@
         <v>13</v>
       </c>
       <c r="F149" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I149" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="150" ht="14.25" customHeight="1">
+      <c r="I149" s="4">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="150" ht="14.25" customHeight="1" spans="1:9">
       <c r="A150" s="2" t="s">
         <v>318</v>
       </c>
@@ -5912,16 +6780,16 @@
         <v>13</v>
       </c>
       <c r="F150" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I150" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="151" ht="14.25" customHeight="1">
+      <c r="I150" s="4">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="151" ht="14.25" customHeight="1" spans="1:9">
       <c r="A151" s="2" t="s">
         <v>318</v>
       </c>
@@ -5938,23 +6806,23 @@
         <v>40</v>
       </c>
       <c r="F151" s="2">
-        <v>2500.0</v>
+        <v>2500</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I151" s="2">
-        <v>487.0</v>
-      </c>
-    </row>
-    <row r="152" ht="14.25" customHeight="1">
+      <c r="I151" s="4">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="152" ht="14.25" customHeight="1" spans="1:9">
       <c r="A152" s="2" t="s">
         <v>318</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C152" s="3" t="s">
+      <c r="C152" t="s">
         <v>212</v>
       </c>
       <c r="D152" s="2" t="s">
@@ -5964,16 +6832,16 @@
         <v>13</v>
       </c>
       <c r="F152" s="2">
-        <v>15000.0</v>
+        <v>15000</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I152" s="2">
-        <v>2925.0</v>
-      </c>
-    </row>
-    <row r="153" ht="14.25" customHeight="1">
+      <c r="I152" s="4">
+        <v>2965</v>
+      </c>
+    </row>
+    <row r="153" ht="14.25" customHeight="1" spans="1:9">
       <c r="A153" s="2" t="s">
         <v>327</v>
       </c>
@@ -5990,16 +6858,16 @@
         <v>13</v>
       </c>
       <c r="F153" s="2">
-        <v>2050.0</v>
+        <v>2050</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I153" s="2">
-        <v>399.0</v>
-      </c>
-    </row>
-    <row r="154" ht="14.25" customHeight="1">
+      <c r="I153" s="4">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="154" ht="14.25" customHeight="1" spans="1:9">
       <c r="A154" s="2" t="s">
         <v>327</v>
       </c>
@@ -6016,16 +6884,16 @@
         <v>13</v>
       </c>
       <c r="F154" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I154" s="2">
-        <v>97.0</v>
-      </c>
-    </row>
-    <row r="155" ht="14.25" customHeight="1">
+      <c r="I154" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="155" ht="14.25" customHeight="1" spans="1:9">
       <c r="A155" s="2" t="s">
         <v>327</v>
       </c>
@@ -6042,16 +6910,16 @@
         <v>13</v>
       </c>
       <c r="F155" s="2">
-        <v>15000.0</v>
+        <v>15000</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I155" s="2">
-        <v>2925.0</v>
-      </c>
-    </row>
-    <row r="156" ht="14.25" customHeight="1">
+      <c r="I155" s="4">
+        <v>2947</v>
+      </c>
+    </row>
+    <row r="156" ht="14.25" customHeight="1" spans="1:9">
       <c r="A156" s="2" t="s">
         <v>327</v>
       </c>
@@ -6068,16 +6936,16 @@
         <v>13</v>
       </c>
       <c r="F156" s="2">
-        <v>10000.0</v>
+        <v>10000</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I156" s="2">
-        <v>1950.0</v>
-      </c>
-    </row>
-    <row r="157" ht="14.25" customHeight="1">
+      <c r="I156" s="4">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="157" ht="14.25" customHeight="1" spans="1:9">
       <c r="A157" s="2" t="s">
         <v>332</v>
       </c>
@@ -6094,16 +6962,16 @@
         <v>13</v>
       </c>
       <c r="F157" s="2">
-        <v>20000.0</v>
+        <v>20000</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I157" s="2">
-        <v>3900.0</v>
-      </c>
-    </row>
-    <row r="158" ht="14.25" customHeight="1">
+      <c r="I157" s="4">
+        <v>3823</v>
+      </c>
+    </row>
+    <row r="158" ht="14.25" customHeight="1" spans="1:9">
       <c r="A158" s="2" t="s">
         <v>332</v>
       </c>
@@ -6120,16 +6988,16 @@
         <v>13</v>
       </c>
       <c r="F158" s="2">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I158" s="2">
-        <v>585.0</v>
-      </c>
-    </row>
-    <row r="159" ht="14.25" customHeight="1">
+      <c r="I158" s="4">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="159" ht="14.25" customHeight="1" spans="1:9">
       <c r="A159" s="2" t="s">
         <v>336</v>
       </c>
@@ -6146,16 +7014,16 @@
         <v>13</v>
       </c>
       <c r="F159" s="2">
-        <v>40000.0</v>
+        <v>40000</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I159" s="2">
-        <v>7800.0</v>
-      </c>
-    </row>
-    <row r="160" ht="14.25" customHeight="1">
+      <c r="I159" s="4">
+        <v>7919</v>
+      </c>
+    </row>
+    <row r="160" ht="14.25" customHeight="1" spans="1:9">
       <c r="A160" s="2" t="s">
         <v>338</v>
       </c>
@@ -6172,16 +7040,16 @@
         <v>13</v>
       </c>
       <c r="F160" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I160" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="161" ht="14.25" customHeight="1">
+      <c r="I160" s="4">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="161" ht="14.25" customHeight="1" spans="1:9">
       <c r="A161" s="2" t="s">
         <v>339</v>
       </c>
@@ -6198,16 +7066,16 @@
         <v>13</v>
       </c>
       <c r="F161" s="2">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I161" s="2">
-        <v>585.0</v>
-      </c>
-    </row>
-    <row r="162" ht="14.25" customHeight="1">
+      <c r="I161" s="4">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="162" ht="14.25" customHeight="1" spans="1:9">
       <c r="A162" s="2" t="s">
         <v>342</v>
       </c>
@@ -6224,16 +7092,16 @@
         <v>13</v>
       </c>
       <c r="F162" s="2">
-        <v>10000.0</v>
+        <v>10000</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I162" s="2">
-        <v>1950.0</v>
-      </c>
-    </row>
-    <row r="163" ht="14.25" customHeight="1">
+      <c r="I162" s="4">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="163" ht="14.25" customHeight="1" spans="1:9">
       <c r="A163" s="2" t="s">
         <v>343</v>
       </c>
@@ -6250,16 +7118,16 @@
         <v>13</v>
       </c>
       <c r="F163" s="2">
-        <v>45000.0</v>
+        <v>45000</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I163" s="2">
-        <v>8775.0</v>
-      </c>
-    </row>
-    <row r="164" ht="14.25" customHeight="1">
+      <c r="I163" s="4">
+        <v>8981</v>
+      </c>
+    </row>
+    <row r="164" ht="14.25" customHeight="1" spans="1:9">
       <c r="A164" s="2" t="s">
         <v>344</v>
       </c>
@@ -6276,16 +7144,16 @@
         <v>13</v>
       </c>
       <c r="F164" s="2">
-        <v>4000.0</v>
+        <v>4000</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I164" s="2">
-        <v>780.0</v>
-      </c>
-    </row>
-    <row r="165" ht="14.25" customHeight="1">
+      <c r="I164" s="4">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="165" ht="14.25" customHeight="1" spans="1:9">
       <c r="A165" s="2" t="s">
         <v>347</v>
       </c>
@@ -6302,16 +7170,16 @@
         <v>13</v>
       </c>
       <c r="F165" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I165" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="166" ht="14.25" customHeight="1">
+      <c r="I165" s="4">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="166" ht="14.25" customHeight="1" spans="1:9">
       <c r="A166" s="2" t="s">
         <v>349</v>
       </c>
@@ -6328,16 +7196,16 @@
         <v>13</v>
       </c>
       <c r="F166" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I166" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="167" ht="14.25" customHeight="1">
+      <c r="I166" s="4">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="167" ht="14.25" customHeight="1" spans="1:9">
       <c r="A167" s="2" t="s">
         <v>351</v>
       </c>
@@ -6354,16 +7222,16 @@
         <v>13</v>
       </c>
       <c r="F167" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I167" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="168" ht="14.25" customHeight="1">
+      <c r="I167" s="4">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="168" ht="14.25" customHeight="1" spans="1:9">
       <c r="A168" s="2" t="s">
         <v>353</v>
       </c>
@@ -6380,16 +7248,16 @@
         <v>13</v>
       </c>
       <c r="F168" s="2">
-        <v>15000.0</v>
+        <v>15000</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I168" s="2">
-        <v>2925.0</v>
-      </c>
-    </row>
-    <row r="169" ht="14.25" customHeight="1">
+      <c r="I168" s="4">
+        <v>2847</v>
+      </c>
+    </row>
+    <row r="169" ht="14.25" customHeight="1" spans="1:9">
       <c r="A169" s="2" t="s">
         <v>355</v>
       </c>
@@ -6406,16 +7274,16 @@
         <v>13</v>
       </c>
       <c r="F169" s="2">
-        <v>10000.0</v>
+        <v>10000</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I169" s="2">
-        <v>1950.0</v>
-      </c>
-    </row>
-    <row r="170" ht="14.25" customHeight="1">
+      <c r="I169" s="4">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="170" ht="14.25" customHeight="1" spans="1:9">
       <c r="A170" s="2" t="s">
         <v>357</v>
       </c>
@@ -6428,20 +7296,20 @@
       <c r="D170" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E170" s="3" t="s">
+      <c r="E170" t="s">
         <v>40</v>
       </c>
       <c r="F170" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I170" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="171" ht="14.25" customHeight="1">
+      <c r="I170" s="4">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="171" ht="14.25" customHeight="1" spans="1:9">
       <c r="A171" s="2" t="s">
         <v>359</v>
       </c>
@@ -6458,16 +7326,16 @@
         <v>13</v>
       </c>
       <c r="F171" s="2">
-        <v>10000.0</v>
+        <v>10000</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I171" s="2">
-        <v>1950.0</v>
-      </c>
-    </row>
-    <row r="172" ht="14.25" customHeight="1">
+      <c r="I171" s="4">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="172" ht="14.25" customHeight="1" spans="1:9">
       <c r="A172" s="2" t="s">
         <v>359</v>
       </c>
@@ -6484,16 +7352,16 @@
         <v>13</v>
       </c>
       <c r="F172" s="2">
-        <v>30000.0</v>
+        <v>30000</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I172" s="2">
-        <v>5850.0</v>
-      </c>
-    </row>
-    <row r="173" ht="14.25" customHeight="1">
+      <c r="I172" s="4">
+        <v>5965</v>
+      </c>
+    </row>
+    <row r="173" ht="14.25" customHeight="1" spans="1:9">
       <c r="A173" s="2" t="s">
         <v>362</v>
       </c>
@@ -6510,16 +7378,16 @@
         <v>13</v>
       </c>
       <c r="F173" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I173" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="174" ht="14.25" customHeight="1">
+      <c r="I173" s="4">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="174" ht="14.25" customHeight="1" spans="1:9">
       <c r="A174" s="2" t="s">
         <v>362</v>
       </c>
@@ -6536,16 +7404,16 @@
         <v>13</v>
       </c>
       <c r="F174" s="2">
-        <v>30000.0</v>
+        <v>30000</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I174" s="2">
-        <v>5850.0</v>
-      </c>
-    </row>
-    <row r="175" ht="14.25" customHeight="1">
+      <c r="I174" s="4">
+        <v>5947</v>
+      </c>
+    </row>
+    <row r="175" ht="14.25" customHeight="1" spans="1:9">
       <c r="A175" s="2" t="s">
         <v>365</v>
       </c>
@@ -6562,16 +7430,16 @@
         <v>13</v>
       </c>
       <c r="F175" s="2">
-        <v>2500.0</v>
+        <v>2500</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I175" s="2">
-        <v>487.0</v>
-      </c>
-    </row>
-    <row r="176" ht="14.25" customHeight="1">
+      <c r="I175" s="4">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="176" ht="14.25" customHeight="1" spans="1:9">
       <c r="A176" s="2" t="s">
         <v>365</v>
       </c>
@@ -6588,16 +7456,16 @@
         <v>13</v>
       </c>
       <c r="F176" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I176" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="177" ht="14.25" customHeight="1">
+      <c r="I176" s="4">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="177" ht="14.25" customHeight="1" spans="1:9">
       <c r="A177" s="2" t="s">
         <v>368</v>
       </c>
@@ -6614,16 +7482,16 @@
         <v>13</v>
       </c>
       <c r="F177" s="2">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I177" s="2">
-        <v>585.0</v>
-      </c>
-    </row>
-    <row r="178" ht="14.25" customHeight="1">
+      <c r="I177" s="4">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="178" ht="14.25" customHeight="1" spans="1:9">
       <c r="A178" s="2" t="s">
         <v>370</v>
       </c>
@@ -6640,16 +7508,16 @@
         <v>13</v>
       </c>
       <c r="F178" s="2">
-        <v>30000.0</v>
+        <v>30000</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I178" s="2">
-        <v>5850.0</v>
-      </c>
-    </row>
-    <row r="179" ht="14.25" customHeight="1">
+      <c r="I178" s="4">
+        <v>5711</v>
+      </c>
+    </row>
+    <row r="179" ht="14.25" customHeight="1" spans="1:9">
       <c r="A179" s="2" t="s">
         <v>372</v>
       </c>
@@ -6666,16 +7534,16 @@
         <v>40</v>
       </c>
       <c r="F179" s="2">
-        <v>3500.0</v>
+        <v>3500</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I179" s="2">
-        <v>682.0</v>
-      </c>
-    </row>
-    <row r="180" ht="14.25" customHeight="1">
+      <c r="I179" s="4">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="180" ht="14.25" customHeight="1" spans="1:9">
       <c r="A180" s="2" t="s">
         <v>375</v>
       </c>
@@ -6692,16 +7560,16 @@
         <v>13</v>
       </c>
       <c r="F180" s="2">
-        <v>50000.0</v>
+        <v>50000</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I180" s="2">
-        <v>9750.0</v>
-      </c>
-    </row>
-    <row r="181" ht="14.25" customHeight="1">
+      <c r="I180" s="4">
+        <v>9704</v>
+      </c>
+    </row>
+    <row r="181" ht="14.25" customHeight="1" spans="1:9">
       <c r="A181" s="2" t="s">
         <v>377</v>
       </c>
@@ -6718,16 +7586,16 @@
         <v>13</v>
       </c>
       <c r="F181" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I181" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="182" ht="14.25" customHeight="1">
+      <c r="I181" s="4">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="182" ht="14.25" customHeight="1" spans="1:9">
       <c r="A182" s="2" t="s">
         <v>379</v>
       </c>
@@ -6744,16 +7612,16 @@
         <v>383</v>
       </c>
       <c r="F182" s="2">
-        <v>300.0</v>
+        <v>300</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I182" s="2">
-        <v>58.5</v>
-      </c>
-    </row>
-    <row r="183" ht="14.25" customHeight="1">
+      <c r="I182" s="4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="183" ht="14.25" customHeight="1" spans="1:9">
       <c r="A183" s="2" t="s">
         <v>384</v>
       </c>
@@ -6770,16 +7638,16 @@
         <v>13</v>
       </c>
       <c r="F183" s="2">
-        <v>10000.0</v>
+        <v>10000</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I183" s="2">
-        <v>1950.0</v>
-      </c>
-    </row>
-    <row r="184" ht="14.25" customHeight="1">
+      <c r="I183" s="4">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="184" ht="14.25" customHeight="1" spans="1:9">
       <c r="A184" s="2" t="s">
         <v>385</v>
       </c>
@@ -6796,16 +7664,16 @@
         <v>13</v>
       </c>
       <c r="F184" s="2">
-        <v>150.0</v>
+        <v>150</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I184" s="2">
-        <v>29.0</v>
-      </c>
-    </row>
-    <row r="185" ht="14.25" customHeight="1">
+      <c r="I184" s="4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="185" ht="14.25" customHeight="1" spans="1:9">
       <c r="A185" s="2" t="s">
         <v>388</v>
       </c>
@@ -6822,16 +7690,16 @@
         <v>23</v>
       </c>
       <c r="F185" s="2">
-        <v>1500.0</v>
+        <v>1500</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I185" s="2">
-        <v>292.0</v>
-      </c>
-    </row>
-    <row r="186" ht="14.25" customHeight="1">
+      <c r="I185" s="4">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="186" ht="14.25" customHeight="1" spans="1:9">
       <c r="A186" s="2" t="s">
         <v>390</v>
       </c>
@@ -6848,16 +7716,16 @@
         <v>13</v>
       </c>
       <c r="F186" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I186" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="187" ht="14.25" customHeight="1">
+      <c r="I186" s="4">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="187" ht="14.25" customHeight="1" spans="1:9">
       <c r="A187" s="2" t="s">
         <v>393</v>
       </c>
@@ -6874,16 +7742,16 @@
         <v>13</v>
       </c>
       <c r="F187" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I187" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="188" ht="14.25" customHeight="1">
+      <c r="I187" s="4">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="188" ht="14.25" customHeight="1" spans="1:9">
       <c r="A188" s="2" t="s">
         <v>395</v>
       </c>
@@ -6900,16 +7768,16 @@
         <v>13</v>
       </c>
       <c r="F188" s="2">
-        <v>4000.0</v>
+        <v>4000</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I188" s="2">
-        <v>780.0</v>
-      </c>
-    </row>
-    <row r="189" ht="14.25" customHeight="1">
+      <c r="I188" s="4">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="189" ht="14.25" customHeight="1" spans="1:9">
       <c r="A189" s="2" t="s">
         <v>397</v>
       </c>
@@ -6926,16 +7794,16 @@
         <v>13</v>
       </c>
       <c r="F189" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I189" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="190" ht="14.25" customHeight="1">
+      <c r="I189" s="4">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="190" ht="14.25" customHeight="1" spans="1:9">
       <c r="A190" s="2" t="s">
         <v>397</v>
       </c>
@@ -6952,16 +7820,16 @@
         <v>13</v>
       </c>
       <c r="F190" s="2">
-        <v>5500.0</v>
+        <v>5500</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I190" s="2">
-        <v>1072.0</v>
-      </c>
-    </row>
-    <row r="191" ht="14.25" customHeight="1">
+      <c r="I190" s="4">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="191" ht="14.25" customHeight="1" spans="1:9">
       <c r="A191" s="2" t="s">
         <v>397</v>
       </c>
@@ -6978,16 +7846,16 @@
         <v>13</v>
       </c>
       <c r="F191" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I191" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="192" ht="14.25" customHeight="1">
+      <c r="I191" s="4">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="192" ht="14.25" customHeight="1" spans="1:9">
       <c r="A192" s="2" t="s">
         <v>401</v>
       </c>
@@ -7004,16 +7872,16 @@
         <v>13</v>
       </c>
       <c r="F192" s="2">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I192" s="2">
-        <v>25.0</v>
-      </c>
-    </row>
-    <row r="193" ht="14.25" customHeight="1">
+      <c r="I192" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="193" ht="14.25" customHeight="1" spans="1:9">
       <c r="A193" s="2" t="s">
         <v>403</v>
       </c>
@@ -7030,16 +7898,16 @@
         <v>13</v>
       </c>
       <c r="F193" s="2">
-        <v>4000.0</v>
+        <v>4000</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I193" s="2">
-        <v>780.0</v>
-      </c>
-    </row>
-    <row r="194" ht="14.25" customHeight="1">
+      <c r="I193" s="4">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="194" ht="14.25" customHeight="1" spans="1:9">
       <c r="A194" s="2" t="s">
         <v>403</v>
       </c>
@@ -7056,16 +7924,16 @@
         <v>13</v>
       </c>
       <c r="F194" s="2">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I194" s="2">
-        <v>585.0</v>
-      </c>
-    </row>
-    <row r="195" ht="14.25" customHeight="1">
+      <c r="I194" s="4">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="195" ht="14.25" customHeight="1" spans="1:9">
       <c r="A195" s="2" t="s">
         <v>408</v>
       </c>
@@ -7082,16 +7950,16 @@
         <v>13</v>
       </c>
       <c r="F195" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I195" s="2">
-        <v>148.0</v>
-      </c>
-    </row>
-    <row r="196" ht="14.25" customHeight="1">
+      <c r="I195" s="4">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="196" ht="14.25" customHeight="1" spans="1:9">
       <c r="A196" s="2" t="s">
         <v>408</v>
       </c>
@@ -7108,16 +7976,16 @@
         <v>13</v>
       </c>
       <c r="F196" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I196" s="2">
-        <v>132.0</v>
-      </c>
-    </row>
-    <row r="197" ht="14.25" customHeight="1">
+      <c r="I196" s="4">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="197" ht="14.25" customHeight="1" spans="1:9">
       <c r="A197" s="2" t="s">
         <v>408</v>
       </c>
@@ -7134,16 +8002,16 @@
         <v>13</v>
       </c>
       <c r="F197" s="2">
-        <v>800.0</v>
+        <v>800</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I197" s="2">
-        <v>156.0</v>
-      </c>
-    </row>
-    <row r="198" ht="14.25" customHeight="1">
+      <c r="I197" s="4">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="198" ht="14.25" customHeight="1" spans="1:9">
       <c r="A198" s="2" t="s">
         <v>408</v>
       </c>
@@ -7160,16 +8028,16 @@
         <v>13</v>
       </c>
       <c r="F198" s="2">
-        <v>2800.0</v>
+        <v>2800</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I198" s="2">
-        <v>546.0</v>
-      </c>
-    </row>
-    <row r="199" ht="14.25" customHeight="1">
+      <c r="I198" s="4">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="199" ht="14.25" customHeight="1" spans="1:9">
       <c r="A199" s="2" t="s">
         <v>408</v>
       </c>
@@ -7186,16 +8054,16 @@
         <v>13</v>
       </c>
       <c r="F199" s="2">
-        <v>650.0</v>
+        <v>650</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I199" s="2">
-        <v>126.0</v>
-      </c>
-    </row>
-    <row r="200" ht="14.25" customHeight="1">
+      <c r="I199" s="4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="200" ht="14.25" customHeight="1" spans="1:9">
       <c r="A200" s="2" t="s">
         <v>408</v>
       </c>
@@ -7212,16 +8080,16 @@
         <v>13</v>
       </c>
       <c r="F200" s="2">
-        <v>800.0</v>
+        <v>800</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I200" s="2">
-        <v>156.0</v>
-      </c>
-    </row>
-    <row r="201" ht="14.25" customHeight="1">
+      <c r="I200" s="4">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="201" ht="14.25" customHeight="1" spans="1:9">
       <c r="A201" s="2" t="s">
         <v>408</v>
       </c>
@@ -7238,16 +8106,16 @@
         <v>13</v>
       </c>
       <c r="F201" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I201" s="2">
-        <v>123.0</v>
-      </c>
-    </row>
-    <row r="202" ht="14.25" customHeight="1">
+      <c r="I201" s="4">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="202" ht="14.25" customHeight="1" spans="1:9">
       <c r="A202" s="2" t="s">
         <v>408</v>
       </c>
@@ -7264,16 +8132,16 @@
         <v>13</v>
       </c>
       <c r="F202" s="2">
-        <v>650.0</v>
+        <v>650</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I202" s="2">
-        <v>126.0</v>
-      </c>
-    </row>
-    <row r="203" ht="14.25" customHeight="1">
+      <c r="I202" s="4">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="203" ht="14.25" customHeight="1" spans="1:9">
       <c r="A203" s="2" t="s">
         <v>408</v>
       </c>
@@ -7290,16 +8158,16 @@
         <v>13</v>
       </c>
       <c r="F203" s="2">
-        <v>850.0</v>
+        <v>850</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I203" s="2">
-        <v>165.0</v>
-      </c>
-    </row>
-    <row r="204" ht="14.25" customHeight="1">
+      <c r="I203" s="4">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="204" ht="14.25" customHeight="1" spans="1:9">
       <c r="A204" s="2" t="s">
         <v>408</v>
       </c>
@@ -7316,16 +8184,16 @@
         <v>13</v>
       </c>
       <c r="F204" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I204" s="2">
-        <v>233.0</v>
-      </c>
-    </row>
-    <row r="205" ht="14.25" customHeight="1">
+      <c r="I204" s="4">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="205" ht="14.25" customHeight="1" spans="1:9">
       <c r="A205" s="2" t="s">
         <v>408</v>
       </c>
@@ -7342,16 +8210,16 @@
         <v>13</v>
       </c>
       <c r="F205" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I205" s="2">
-        <v>312.0</v>
-      </c>
-    </row>
-    <row r="206" ht="14.25" customHeight="1">
+      <c r="I205" s="4">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="206" ht="14.25" customHeight="1" spans="1:9">
       <c r="A206" s="2" t="s">
         <v>408</v>
       </c>
@@ -7368,16 +8236,16 @@
         <v>13</v>
       </c>
       <c r="F206" s="2">
-        <v>850.0</v>
+        <v>850</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I206" s="2">
-        <v>165.0</v>
-      </c>
-    </row>
-    <row r="207" ht="14.25" customHeight="1">
+      <c r="I206" s="4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="207" ht="14.25" customHeight="1" spans="1:9">
       <c r="A207" s="2" t="s">
         <v>408</v>
       </c>
@@ -7394,16 +8262,16 @@
         <v>13</v>
       </c>
       <c r="F207" s="2">
-        <v>600.0</v>
+        <v>600</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I207" s="2">
-        <v>117.0</v>
-      </c>
-    </row>
-    <row r="208" ht="14.25" customHeight="1">
+      <c r="I207" s="4">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="208" ht="14.25" customHeight="1" spans="1:9">
       <c r="A208" s="2" t="s">
         <v>408</v>
       </c>
@@ -7420,16 +8288,16 @@
         <v>13</v>
       </c>
       <c r="F208" s="2">
-        <v>200.0</v>
+        <v>200</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I208" s="2">
-        <v>39.0</v>
-      </c>
-    </row>
-    <row r="209" ht="14.25" customHeight="1">
+      <c r="I208" s="4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="209" ht="14.25" customHeight="1" spans="1:9">
       <c r="A209" s="2" t="s">
         <v>408</v>
       </c>
@@ -7446,16 +8314,16 @@
         <v>13</v>
       </c>
       <c r="F209" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I209" s="2">
-        <v>95.0</v>
-      </c>
-    </row>
-    <row r="210" ht="14.25" customHeight="1">
+      <c r="I209" s="4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="210" ht="14.25" customHeight="1" spans="1:9">
       <c r="A210" s="2" t="s">
         <v>408</v>
       </c>
@@ -7472,16 +8340,16 @@
         <v>13</v>
       </c>
       <c r="F210" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I210" s="2">
-        <v>97.0</v>
-      </c>
-    </row>
-    <row r="211" ht="14.25" customHeight="1">
+      <c r="I210" s="4">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="211" ht="14.25" customHeight="1" spans="1:9">
       <c r="A211" s="2" t="s">
         <v>408</v>
       </c>
@@ -7498,16 +8366,16 @@
         <v>13</v>
       </c>
       <c r="F211" s="2">
-        <v>850.0</v>
+        <v>850</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I211" s="2">
-        <v>165.0</v>
-      </c>
-    </row>
-    <row r="212" ht="14.25" customHeight="1">
+      <c r="I211" s="4">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="212" ht="14.25" customHeight="1" spans="1:9">
       <c r="A212" s="2" t="s">
         <v>408</v>
       </c>
@@ -7524,16 +8392,16 @@
         <v>13</v>
       </c>
       <c r="F212" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I212" s="2">
-        <v>97.0</v>
-      </c>
-    </row>
-    <row r="213" ht="14.25" customHeight="1">
+      <c r="I212" s="4">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="213" ht="14.25" customHeight="1" spans="1:9">
       <c r="A213" s="2" t="s">
         <v>408</v>
       </c>
@@ -7550,16 +8418,16 @@
         <v>13</v>
       </c>
       <c r="F213" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I213" s="2">
-        <v>97.0</v>
-      </c>
-    </row>
-    <row r="214" ht="14.25" customHeight="1">
+      <c r="I213" s="4">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="214" ht="14.25" customHeight="1" spans="1:9">
       <c r="A214" s="2" t="s">
         <v>408</v>
       </c>
@@ -7576,16 +8444,16 @@
         <v>13</v>
       </c>
       <c r="F214" s="2">
-        <v>1700.0</v>
+        <v>1700</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I214" s="2">
-        <v>331.0</v>
-      </c>
-    </row>
-    <row r="215" ht="14.25" customHeight="1">
+      <c r="I214" s="4">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="215" ht="14.25" customHeight="1" spans="1:9">
       <c r="A215" s="2" t="s">
         <v>408</v>
       </c>
@@ -7602,16 +8470,16 @@
         <v>13</v>
       </c>
       <c r="F215" s="2">
-        <v>2500.0</v>
+        <v>2500</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I215" s="2">
-        <v>487.0</v>
-      </c>
-    </row>
-    <row r="216" ht="14.25" customHeight="1">
+      <c r="I215" s="4">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="216" ht="14.25" customHeight="1" spans="1:9">
       <c r="A216" s="2" t="s">
         <v>408</v>
       </c>
@@ -7628,16 +8496,16 @@
         <v>13</v>
       </c>
       <c r="F216" s="2">
-        <v>850.0</v>
+        <v>850</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I216" s="2">
-        <v>165.0</v>
-      </c>
-    </row>
-    <row r="217" ht="14.25" customHeight="1">
+      <c r="I216" s="4">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="217" ht="14.25" customHeight="1" spans="1:9">
       <c r="A217" s="2" t="s">
         <v>408</v>
       </c>
@@ -7654,16 +8522,16 @@
         <v>13</v>
       </c>
       <c r="F217" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I217" s="2">
-        <v>97.0</v>
-      </c>
-    </row>
-    <row r="218" ht="14.25" customHeight="1">
+      <c r="I217" s="4">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="218" ht="14.25" customHeight="1" spans="1:9">
       <c r="A218" s="2" t="s">
         <v>408</v>
       </c>
@@ -7680,16 +8548,16 @@
         <v>13</v>
       </c>
       <c r="F218" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I218" s="2">
-        <v>94.0</v>
-      </c>
-    </row>
-    <row r="219" ht="14.25" customHeight="1">
+      <c r="I218" s="4">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="219" ht="14.25" customHeight="1" spans="1:9">
       <c r="A219" s="2" t="s">
         <v>408</v>
       </c>
@@ -7706,16 +8574,16 @@
         <v>13</v>
       </c>
       <c r="F219" s="2">
-        <v>700.0</v>
+        <v>700</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I219" s="2">
-        <v>136.0</v>
-      </c>
-    </row>
-    <row r="220" ht="14.25" customHeight="1">
+      <c r="I219" s="4">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="220" ht="14.25" customHeight="1" spans="1:9">
       <c r="A220" s="2" t="s">
         <v>408</v>
       </c>
@@ -7732,16 +8600,16 @@
         <v>13</v>
       </c>
       <c r="F220" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I220" s="2">
-        <v>99.0</v>
-      </c>
-    </row>
-    <row r="221" ht="14.25" customHeight="1">
+      <c r="I220" s="4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="221" ht="14.25" customHeight="1" spans="1:9">
       <c r="A221" s="2" t="s">
         <v>408</v>
       </c>
@@ -7758,16 +8626,16 @@
         <v>13</v>
       </c>
       <c r="F221" s="2">
-        <v>750.0</v>
+        <v>750</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I221" s="2">
-        <v>146.0</v>
-      </c>
-    </row>
-    <row r="222" ht="14.25" customHeight="1">
+      <c r="I221" s="4">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="222" ht="14.25" customHeight="1" spans="1:9">
       <c r="A222" s="2" t="s">
         <v>408</v>
       </c>
@@ -7784,16 +8652,16 @@
         <v>13</v>
       </c>
       <c r="F222" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I222" s="2">
-        <v>91.0</v>
-      </c>
-    </row>
-    <row r="223" ht="14.25" customHeight="1">
+      <c r="I222" s="4">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="223" ht="14.25" customHeight="1" spans="1:9">
       <c r="A223" s="2" t="s">
         <v>408</v>
       </c>
@@ -7810,16 +8678,16 @@
         <v>13</v>
       </c>
       <c r="F223" s="2">
-        <v>250.0</v>
+        <v>250</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I223" s="2">
-        <v>101.0</v>
-      </c>
-    </row>
-    <row r="224" ht="14.25" customHeight="1">
+      <c r="I223" s="4">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="224" ht="14.25" customHeight="1" spans="1:9">
       <c r="A224" s="2" t="s">
         <v>408</v>
       </c>
@@ -7836,16 +8704,16 @@
         <v>13</v>
       </c>
       <c r="F224" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I224" s="2">
-        <v>124.0</v>
-      </c>
-    </row>
-    <row r="225" ht="14.25" customHeight="1">
+      <c r="I224" s="4">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="225" ht="14.25" customHeight="1" spans="1:9">
       <c r="A225" s="2" t="s">
         <v>408</v>
       </c>
@@ -7862,16 +8730,16 @@
         <v>13</v>
       </c>
       <c r="F225" s="2">
-        <v>600.0</v>
+        <v>600</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I225" s="2">
-        <v>117.0</v>
-      </c>
-    </row>
-    <row r="226" ht="14.25" customHeight="1">
+      <c r="I225" s="4">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="226" ht="14.25" customHeight="1" spans="1:9">
       <c r="A226" s="2" t="s">
         <v>408</v>
       </c>
@@ -7888,16 +8756,16 @@
         <v>13</v>
       </c>
       <c r="F226" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I226" s="2">
-        <v>97.0</v>
-      </c>
-    </row>
-    <row r="227" ht="14.25" customHeight="1">
+      <c r="I226" s="4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="227" ht="14.25" customHeight="1" spans="1:9">
       <c r="A227" s="2" t="s">
         <v>408</v>
       </c>
@@ -7914,16 +8782,16 @@
         <v>13</v>
       </c>
       <c r="F227" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I227" s="2">
-        <v>97.0</v>
-      </c>
-    </row>
-    <row r="228" ht="14.25" customHeight="1">
+      <c r="I227" s="4">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="228" ht="14.25" customHeight="1" spans="1:9">
       <c r="A228" s="2" t="s">
         <v>408</v>
       </c>
@@ -7940,16 +8808,16 @@
         <v>13</v>
       </c>
       <c r="F228" s="2">
-        <v>1200.0</v>
+        <v>1200</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I228" s="2">
-        <v>234.0</v>
-      </c>
-    </row>
-    <row r="229" ht="14.25" customHeight="1">
+      <c r="I228" s="4">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="229" ht="14.25" customHeight="1" spans="1:9">
       <c r="A229" s="2" t="s">
         <v>408</v>
       </c>
@@ -7966,16 +8834,16 @@
         <v>13</v>
       </c>
       <c r="F229" s="2">
-        <v>750.0</v>
+        <v>750</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I229" s="2">
-        <v>146.0</v>
-      </c>
-    </row>
-    <row r="230" ht="14.25" customHeight="1">
+      <c r="I229" s="4">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="230" ht="14.25" customHeight="1" spans="1:9">
       <c r="A230" s="2" t="s">
         <v>408</v>
       </c>
@@ -7992,16 +8860,16 @@
         <v>13</v>
       </c>
       <c r="F230" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I230" s="2">
-        <v>97.0</v>
-      </c>
-    </row>
-    <row r="231" ht="14.25" customHeight="1">
+      <c r="I230" s="4">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="231" ht="14.25" customHeight="1" spans="1:9">
       <c r="A231" s="2" t="s">
         <v>408</v>
       </c>
@@ -8018,16 +8886,16 @@
         <v>13</v>
       </c>
       <c r="F231" s="2">
-        <v>800.0</v>
+        <v>800</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I231" s="2">
-        <v>156.0</v>
-      </c>
-    </row>
-    <row r="232" ht="14.25" customHeight="1">
+      <c r="I231" s="4">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="232" ht="14.25" customHeight="1" spans="1:9">
       <c r="A232" s="2" t="s">
         <v>408</v>
       </c>
@@ -8044,16 +8912,16 @@
         <v>13</v>
       </c>
       <c r="F232" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I232" s="2">
-        <v>97.0</v>
-      </c>
-    </row>
-    <row r="233" ht="14.25" customHeight="1">
+      <c r="I232" s="4">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="233" ht="14.25" customHeight="1" spans="1:9">
       <c r="A233" s="2" t="s">
         <v>408</v>
       </c>
@@ -8070,16 +8938,16 @@
         <v>13</v>
       </c>
       <c r="F233" s="2">
-        <v>800.0</v>
+        <v>800</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I233" s="2">
-        <v>156.0</v>
-      </c>
-    </row>
-    <row r="234" ht="14.25" customHeight="1">
+      <c r="I233" s="4">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="234" ht="14.25" customHeight="1" spans="1:9">
       <c r="A234" s="2" t="s">
         <v>408</v>
       </c>
@@ -8096,16 +8964,16 @@
         <v>13</v>
       </c>
       <c r="F234" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I234" s="2">
-        <v>97.0</v>
-      </c>
-    </row>
-    <row r="235" ht="14.25" customHeight="1">
+      <c r="I234" s="4">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="235" ht="14.25" customHeight="1" spans="1:9">
       <c r="A235" s="2" t="s">
         <v>408</v>
       </c>
@@ -8122,16 +8990,16 @@
         <v>13</v>
       </c>
       <c r="F235" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I235" s="2">
-        <v>97.0</v>
-      </c>
-    </row>
-    <row r="236" ht="14.25" customHeight="1">
+      <c r="I235" s="4">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="236" ht="14.25" customHeight="1" spans="1:9">
       <c r="A236" s="2" t="s">
         <v>456</v>
       </c>
@@ -8144,20 +9012,20 @@
       <c r="D236" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E236" s="3" t="s">
+      <c r="E236" t="s">
         <v>23</v>
       </c>
       <c r="F236" s="2">
-        <v>6500.0</v>
+        <v>6500</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I236" s="2">
-        <v>1267.0</v>
-      </c>
-    </row>
-    <row r="237" ht="14.25" customHeight="1">
+      <c r="I236" s="4">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="237" ht="14.25" customHeight="1" spans="1:9">
       <c r="A237" s="2" t="s">
         <v>458</v>
       </c>
@@ -8174,16 +9042,16 @@
         <v>13</v>
       </c>
       <c r="F237" s="2">
-        <v>1500.0</v>
+        <v>1500</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I237" s="2">
-        <v>292.0</v>
-      </c>
-    </row>
-    <row r="238" ht="14.25" customHeight="1">
+      <c r="I237" s="4">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="238" ht="14.25" customHeight="1" spans="1:9">
       <c r="A238" s="2" t="s">
         <v>461</v>
       </c>
@@ -8200,16 +9068,16 @@
         <v>13</v>
       </c>
       <c r="F238" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I238" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="239" ht="14.25" customHeight="1">
+      <c r="I238" s="4">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="239" ht="14.25" customHeight="1" spans="1:9">
       <c r="A239" s="2" t="s">
         <v>464</v>
       </c>
@@ -8226,16 +9094,16 @@
         <v>13</v>
       </c>
       <c r="F239" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I239" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="240" ht="14.25" customHeight="1">
+      <c r="I239" s="4">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="240" ht="14.25" customHeight="1" spans="1:9">
       <c r="A240" s="2" t="s">
         <v>467</v>
       </c>
@@ -8248,20 +9116,20 @@
       <c r="D240" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E240" s="3" t="s">
+      <c r="E240" t="s">
         <v>13</v>
       </c>
       <c r="F240" s="2">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I240" s="2">
-        <v>19.0</v>
-      </c>
-    </row>
-    <row r="241" ht="14.25" customHeight="1">
+      <c r="I240" s="4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="241" ht="14.25" customHeight="1" spans="1:9">
       <c r="A241" s="2" t="s">
         <v>469</v>
       </c>
@@ -8278,16 +9146,16 @@
         <v>13</v>
       </c>
       <c r="F241" s="2">
-        <v>15000.0</v>
+        <v>15000</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I241" s="2">
-        <v>2925.0</v>
-      </c>
-    </row>
-    <row r="242" ht="14.25" customHeight="1">
+      <c r="I241" s="4">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="242" ht="14.25" customHeight="1" spans="1:9">
       <c r="A242" s="2" t="s">
         <v>469</v>
       </c>
@@ -8304,16 +9172,16 @@
         <v>13</v>
       </c>
       <c r="F242" s="2">
-        <v>200.0</v>
+        <v>200</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I242" s="2">
-        <v>39.0</v>
-      </c>
-    </row>
-    <row r="243" ht="14.25" customHeight="1">
+      <c r="I242" s="4">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="243" ht="14.25" customHeight="1" spans="1:9">
       <c r="A243" s="2" t="s">
         <v>472</v>
       </c>
@@ -8330,16 +9198,16 @@
         <v>13</v>
       </c>
       <c r="F243" s="2">
-        <v>6000.0</v>
+        <v>6000</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I243" s="2">
-        <v>1170.0</v>
-      </c>
-    </row>
-    <row r="244" ht="14.25" customHeight="1">
+      <c r="I243" s="4">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="244" ht="14.25" customHeight="1" spans="1:9">
       <c r="A244" s="2" t="s">
         <v>475</v>
       </c>
@@ -8356,16 +9224,16 @@
         <v>13</v>
       </c>
       <c r="F244" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I244" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="245" ht="14.25" customHeight="1">
+      <c r="I244" s="4">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="245" ht="14.25" customHeight="1" spans="1:9">
       <c r="A245" s="2" t="s">
         <v>477</v>
       </c>
@@ -8382,16 +9250,16 @@
         <v>23</v>
       </c>
       <c r="F245" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I245" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="246" ht="14.25" customHeight="1">
+      <c r="I245" s="4">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="246" ht="14.25" customHeight="1" spans="1:9">
       <c r="A246" s="2" t="s">
         <v>480</v>
       </c>
@@ -8408,16 +9276,16 @@
         <v>13</v>
       </c>
       <c r="F246" s="2">
-        <v>350.0</v>
+        <v>350</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I246" s="2">
-        <v>123.0</v>
-      </c>
-    </row>
-    <row r="247" ht="14.25" customHeight="1">
+      <c r="I246" s="4">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="247" ht="14.25" customHeight="1" spans="1:9">
       <c r="A247" s="2" t="s">
         <v>482</v>
       </c>
@@ -8427,23 +9295,23 @@
       <c r="C247" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D247" s="3" t="s">
+      <c r="D247" t="s">
         <v>18</v>
       </c>
       <c r="E247" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F247" s="2">
-        <v>10000.0</v>
+        <v>10000</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I247" s="2">
-        <v>1950.0</v>
-      </c>
-    </row>
-    <row r="248" ht="14.25" customHeight="1">
+      <c r="I247" s="4">
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="248" ht="14.25" customHeight="1" spans="1:9">
       <c r="A248" s="2" t="s">
         <v>482</v>
       </c>
@@ -8460,16 +9328,16 @@
         <v>13</v>
       </c>
       <c r="F248" s="2">
-        <v>2500.0</v>
+        <v>2500</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I248" s="2">
-        <v>487.0</v>
-      </c>
-    </row>
-    <row r="249" ht="14.25" customHeight="1">
+      <c r="I248" s="4">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="249" ht="14.25" customHeight="1" spans="1:9">
       <c r="A249" s="2" t="s">
         <v>482</v>
       </c>
@@ -8486,23 +9354,23 @@
         <v>13</v>
       </c>
       <c r="F249" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I249" s="2">
-        <v>137.0</v>
-      </c>
-    </row>
-    <row r="250" ht="14.25" customHeight="1">
+      <c r="I249" s="4">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="250" ht="14.25" customHeight="1" spans="1:9">
       <c r="A250" s="2" t="s">
         <v>482</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="C250" s="3" t="s">
+      <c r="C250" t="s">
         <v>47</v>
       </c>
       <c r="D250" s="2" t="s">
@@ -8512,16 +9380,16 @@
         <v>13</v>
       </c>
       <c r="F250" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I250" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="251" ht="14.25" customHeight="1">
+      <c r="I250" s="4">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="251" ht="14.25" customHeight="1" spans="1:9">
       <c r="A251" s="2" t="s">
         <v>482</v>
       </c>
@@ -8538,16 +9406,16 @@
         <v>13</v>
       </c>
       <c r="F251" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I251" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="252" ht="14.25" customHeight="1">
+      <c r="I251" s="4">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="252" ht="14.25" customHeight="1" spans="1:9">
       <c r="A252" s="2" t="s">
         <v>482</v>
       </c>
@@ -8564,16 +9432,16 @@
         <v>13</v>
       </c>
       <c r="F252" s="2">
-        <v>2500.0</v>
+        <v>2500</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I252" s="2">
-        <v>484.0</v>
-      </c>
-    </row>
-    <row r="253" ht="14.25" customHeight="1">
+      <c r="I252" s="4">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="253" ht="14.25" customHeight="1" spans="1:9">
       <c r="A253" s="2" t="s">
         <v>482</v>
       </c>
@@ -8590,23 +9458,23 @@
         <v>13</v>
       </c>
       <c r="F253" s="2">
-        <v>2500.0</v>
+        <v>2500</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I253" s="2">
-        <v>457.0</v>
-      </c>
-    </row>
-    <row r="254" ht="14.25" customHeight="1">
+      <c r="I253" s="4">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="254" ht="14.25" customHeight="1" spans="1:9">
       <c r="A254" s="2" t="s">
         <v>482</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="C254" s="3" t="s">
+      <c r="C254" t="s">
         <v>490</v>
       </c>
       <c r="D254" s="2" t="s">
@@ -8616,16 +9484,16 @@
         <v>13</v>
       </c>
       <c r="F254" s="2">
-        <v>2500.0</v>
+        <v>2500</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I254" s="2">
-        <v>435.0</v>
-      </c>
-    </row>
-    <row r="255" ht="14.25" customHeight="1">
+      <c r="I254" s="4">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="255" ht="14.25" customHeight="1" spans="1:9">
       <c r="A255" s="2" t="s">
         <v>494</v>
       </c>
@@ -8642,16 +9510,16 @@
         <v>23</v>
       </c>
       <c r="F255" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I255" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="256" ht="14.25" customHeight="1">
+      <c r="I255" s="4">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="256" ht="14.25" customHeight="1" spans="1:9">
       <c r="A256" s="2" t="s">
         <v>494</v>
       </c>
@@ -8668,16 +9536,16 @@
         <v>13</v>
       </c>
       <c r="F256" s="2">
-        <v>1500.0</v>
+        <v>1500</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I256" s="2">
-        <v>223.0</v>
-      </c>
-    </row>
-    <row r="257" ht="14.25" customHeight="1">
+      <c r="I256" s="4">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="257" ht="14.25" customHeight="1" spans="1:9">
       <c r="A257" s="2" t="s">
         <v>494</v>
       </c>
@@ -8694,16 +9562,16 @@
         <v>23</v>
       </c>
       <c r="F257" s="2">
-        <v>1500.0</v>
+        <v>1500</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I257" s="2">
-        <v>292.0</v>
-      </c>
-    </row>
-    <row r="258" ht="14.25" customHeight="1">
+      <c r="I257" s="4">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="258" ht="14.25" customHeight="1" spans="1:9">
       <c r="A258" s="2" t="s">
         <v>499</v>
       </c>
@@ -8720,16 +9588,16 @@
         <v>13</v>
       </c>
       <c r="F258" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I258" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="259" ht="14.25" customHeight="1">
+      <c r="I258" s="4">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="259" ht="14.25" customHeight="1" spans="1:9">
       <c r="A259" s="2" t="s">
         <v>499</v>
       </c>
@@ -8746,16 +9614,16 @@
         <v>13</v>
       </c>
       <c r="F259" s="2">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I259" s="2">
-        <v>29.0</v>
-      </c>
-    </row>
-    <row r="260" ht="14.25" customHeight="1">
+      <c r="I259" s="4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="260" ht="14.25" customHeight="1" spans="1:9">
       <c r="A260" s="2" t="s">
         <v>502</v>
       </c>
@@ -8772,16 +9640,16 @@
         <v>13</v>
       </c>
       <c r="F260" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I260" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="261" ht="14.25" customHeight="1">
+      <c r="I260" s="4">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="261" ht="14.25" customHeight="1" spans="1:9">
       <c r="A261" s="2" t="s">
         <v>502</v>
       </c>
@@ -8798,16 +9666,16 @@
         <v>13</v>
       </c>
       <c r="F261" s="2">
-        <v>6000.0</v>
+        <v>6000</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I261" s="2">
-        <v>1170.0</v>
-      </c>
-    </row>
-    <row r="262" ht="14.25" customHeight="1">
+      <c r="I261" s="4">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="262" ht="14.25" customHeight="1" spans="1:9">
       <c r="A262" s="2" t="s">
         <v>506</v>
       </c>
@@ -8824,16 +9692,16 @@
         <v>13</v>
       </c>
       <c r="F262" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I262" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="263" ht="14.25" customHeight="1">
+      <c r="I262" s="4">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="263" ht="14.25" customHeight="1" spans="1:9">
       <c r="A263" s="2" t="s">
         <v>506</v>
       </c>
@@ -8850,16 +9718,16 @@
         <v>13</v>
       </c>
       <c r="F263" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I263" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="264" ht="14.25" customHeight="1">
+      <c r="I263" s="4">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="264" ht="14.25" customHeight="1" spans="1:9">
       <c r="A264" s="2" t="s">
         <v>506</v>
       </c>
@@ -8876,16 +9744,16 @@
         <v>13</v>
       </c>
       <c r="F264" s="2">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I264" s="2">
-        <v>56.0</v>
-      </c>
-    </row>
-    <row r="265" ht="14.25" customHeight="1">
+      <c r="I264" s="4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="265" ht="14.25" customHeight="1" spans="1:9">
       <c r="A265" s="2" t="s">
         <v>506</v>
       </c>
@@ -8902,16 +9770,16 @@
         <v>13</v>
       </c>
       <c r="F265" s="2">
-        <v>1500.0</v>
+        <v>1500</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I265" s="2">
-        <v>294.0</v>
-      </c>
-    </row>
-    <row r="266" ht="14.25" customHeight="1">
+      <c r="I265" s="4">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="266" ht="14.25" customHeight="1" spans="1:9">
       <c r="A266" s="2" t="s">
         <v>506</v>
       </c>
@@ -8928,16 +9796,16 @@
         <v>13</v>
       </c>
       <c r="F266" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I266" s="2">
-        <v>99.0</v>
-      </c>
-    </row>
-    <row r="267" ht="14.25" customHeight="1">
+      <c r="I266" s="4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="267" ht="14.25" customHeight="1" spans="1:9">
       <c r="A267" s="2" t="s">
         <v>506</v>
       </c>
@@ -8954,16 +9822,16 @@
         <v>13</v>
       </c>
       <c r="F267" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I267" s="2">
-        <v>301.0</v>
-      </c>
-    </row>
-    <row r="268" ht="14.25" customHeight="1">
+      <c r="I267" s="4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="268" ht="14.25" customHeight="1" spans="1:9">
       <c r="A268" s="2" t="s">
         <v>506</v>
       </c>
@@ -8980,16 +9848,16 @@
         <v>13</v>
       </c>
       <c r="F268" s="2">
-        <v>1500.0</v>
+        <v>1500</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I268" s="2">
-        <v>259.0</v>
-      </c>
-    </row>
-    <row r="269" ht="14.25" customHeight="1">
+      <c r="I268" s="4">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="269" ht="14.25" customHeight="1" spans="1:9">
       <c r="A269" s="2" t="s">
         <v>506</v>
       </c>
@@ -9006,16 +9874,16 @@
         <v>13</v>
       </c>
       <c r="F269" s="2">
-        <v>1500.0</v>
+        <v>1500</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I269" s="2">
-        <v>237.0</v>
-      </c>
-    </row>
-    <row r="270" ht="14.25" customHeight="1">
+      <c r="I269" s="4">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="270" ht="14.25" customHeight="1" spans="1:9">
       <c r="A270" s="2" t="s">
         <v>518</v>
       </c>
@@ -9032,16 +9900,16 @@
         <v>40</v>
       </c>
       <c r="F270" s="2">
-        <v>1500.0</v>
+        <v>1500</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I270" s="2">
-        <v>292.0</v>
-      </c>
-    </row>
-    <row r="271" ht="14.25" customHeight="1">
+      <c r="I270" s="4">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="271" ht="14.25" customHeight="1" spans="1:9">
       <c r="A271" s="2" t="s">
         <v>520</v>
       </c>
@@ -9058,16 +9926,16 @@
         <v>40</v>
       </c>
       <c r="F271" s="2">
-        <v>2500.0</v>
+        <v>2500</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I271" s="2">
-        <v>487.0</v>
-      </c>
-    </row>
-    <row r="272" ht="14.25" customHeight="1">
+      <c r="I271" s="4">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="272" ht="14.25" customHeight="1" spans="1:9">
       <c r="A272" s="2" t="s">
         <v>523</v>
       </c>
@@ -9084,16 +9952,16 @@
         <v>13</v>
       </c>
       <c r="F272" s="2">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I272" s="2">
-        <v>585.0</v>
-      </c>
-    </row>
-    <row r="273" ht="14.25" customHeight="1">
+      <c r="I272" s="4">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="273" ht="14.25" customHeight="1" spans="1:9">
       <c r="A273" s="2" t="s">
         <v>523</v>
       </c>
@@ -9110,16 +9978,16 @@
         <v>13</v>
       </c>
       <c r="F273" s="2">
-        <v>13000.0</v>
+        <v>13000</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I273" s="2">
-        <v>2535.0</v>
-      </c>
-    </row>
-    <row r="274" ht="14.25" customHeight="1">
+      <c r="I273" s="4">
+        <v>2540</v>
+      </c>
+    </row>
+    <row r="274" ht="14.25" customHeight="1" spans="1:9">
       <c r="A274" s="2" t="s">
         <v>526</v>
       </c>
@@ -9136,16 +10004,16 @@
         <v>13</v>
       </c>
       <c r="F274" s="2">
-        <v>1500.0</v>
+        <v>1500</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I274" s="2">
-        <v>222.0</v>
-      </c>
-    </row>
-    <row r="275" ht="14.25" customHeight="1">
+      <c r="I274" s="4">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="275" ht="14.25" customHeight="1" spans="1:9">
       <c r="A275" s="2" t="s">
         <v>528</v>
       </c>
@@ -9162,16 +10030,16 @@
         <v>13</v>
       </c>
       <c r="F275" s="2">
-        <v>6000.0</v>
+        <v>6000</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I275" s="2">
-        <v>1170.0</v>
-      </c>
-    </row>
-    <row r="276" ht="14.25" customHeight="1">
+      <c r="I275" s="4">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="276" ht="14.25" customHeight="1" spans="1:9">
       <c r="A276" s="2" t="s">
         <v>529</v>
       </c>
@@ -9188,16 +10056,16 @@
         <v>13</v>
       </c>
       <c r="F276" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I276" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="277" ht="14.25" customHeight="1">
+      <c r="I276" s="4">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="277" ht="14.25" customHeight="1" spans="1:9">
       <c r="A277" s="2" t="s">
         <v>531</v>
       </c>
@@ -9214,16 +10082,16 @@
         <v>13</v>
       </c>
       <c r="F277" s="2">
-        <v>10000.0</v>
+        <v>10000</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I277" s="2">
-        <v>1950.0</v>
-      </c>
-    </row>
-    <row r="278" ht="14.25" customHeight="1">
+      <c r="I277" s="4">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="278" ht="14.25" customHeight="1" spans="1:9">
       <c r="A278" s="2" t="s">
         <v>531</v>
       </c>
@@ -9240,16 +10108,16 @@
         <v>13</v>
       </c>
       <c r="F278" s="2">
-        <v>7000.0</v>
+        <v>7000</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I278" s="2">
-        <v>1365.0</v>
-      </c>
-    </row>
-    <row r="279" ht="14.25" customHeight="1">
+      <c r="I278" s="4">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="279" ht="14.25" customHeight="1" spans="1:9">
       <c r="A279" s="2" t="s">
         <v>531</v>
       </c>
@@ -9266,16 +10134,16 @@
         <v>311</v>
       </c>
       <c r="F279" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I279" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="280" ht="14.25" customHeight="1">
+      <c r="I279" s="4">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="280" ht="14.25" customHeight="1" spans="1:9">
       <c r="A280" s="2" t="s">
         <v>538</v>
       </c>
@@ -9292,16 +10160,16 @@
         <v>13</v>
       </c>
       <c r="F280" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I280" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="281" ht="14.25" customHeight="1">
+      <c r="I280" s="4">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="281" ht="14.25" customHeight="1" spans="1:9">
       <c r="A281" s="2" t="s">
         <v>538</v>
       </c>
@@ -9318,16 +10186,16 @@
         <v>13</v>
       </c>
       <c r="F281" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I281" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="282" ht="14.25" customHeight="1">
+      <c r="I281" s="4">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="282" ht="14.25" customHeight="1" spans="1:9">
       <c r="A282" s="2" t="s">
         <v>542</v>
       </c>
@@ -9344,16 +10212,16 @@
         <v>383</v>
       </c>
       <c r="F282" s="2">
-        <v>1500.0</v>
+        <v>1500</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I282" s="2">
-        <v>299.0</v>
-      </c>
-    </row>
-    <row r="283" ht="14.25" customHeight="1">
+      <c r="I282" s="4">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="283" ht="14.25" customHeight="1" spans="1:9">
       <c r="A283" s="2" t="s">
         <v>542</v>
       </c>
@@ -9370,16 +10238,16 @@
         <v>548</v>
       </c>
       <c r="F283" s="2">
-        <v>30000.0</v>
+        <v>30000</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I283" s="2">
-        <v>5850.0</v>
-      </c>
-    </row>
-    <row r="284" ht="14.25" customHeight="1">
+      <c r="I283" s="4">
+        <v>5950</v>
+      </c>
+    </row>
+    <row r="284" ht="14.25" customHeight="1" spans="1:9">
       <c r="A284" s="2" t="s">
         <v>549</v>
       </c>
@@ -9396,16 +10264,16 @@
         <v>23</v>
       </c>
       <c r="F284" s="2">
-        <v>10000.0</v>
+        <v>10000</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I284" s="2">
-        <v>1950.0</v>
-      </c>
-    </row>
-    <row r="285" ht="14.25" customHeight="1">
+      <c r="I284" s="4">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="285" ht="14.25" customHeight="1" spans="1:9">
       <c r="A285" s="2" t="s">
         <v>549</v>
       </c>
@@ -9422,16 +10290,16 @@
         <v>13</v>
       </c>
       <c r="F285" s="2">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I285" s="2">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="286" ht="14.25" customHeight="1">
+      <c r="I285" s="4">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="286" ht="14.25" customHeight="1" spans="1:9">
       <c r="A286" s="2" t="s">
         <v>553</v>
       </c>
@@ -9448,16 +10316,16 @@
         <v>13</v>
       </c>
       <c r="F286" s="2">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I286" s="2">
-        <v>975.0</v>
-      </c>
-    </row>
-    <row r="287" ht="14.25" customHeight="1">
+      <c r="I286" s="4">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="287" ht="14.25" customHeight="1" spans="1:9">
       <c r="A287" s="2" t="s">
         <v>553</v>
       </c>
@@ -9474,16 +10342,16 @@
         <v>23</v>
       </c>
       <c r="F287" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I287" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="288" ht="14.25" customHeight="1">
+      <c r="I287" s="4">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="288" ht="14.25" customHeight="1" spans="1:9">
       <c r="A288" s="2" t="s">
         <v>557</v>
       </c>
@@ -9500,16 +10368,16 @@
         <v>23</v>
       </c>
       <c r="F288" s="2">
-        <v>20000.0</v>
+        <v>20000</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I288" s="2">
-        <v>3900.0</v>
-      </c>
-    </row>
-    <row r="289" ht="14.25" customHeight="1">
+      <c r="I288" s="4">
+        <v>3877</v>
+      </c>
+    </row>
+    <row r="289" ht="14.25" customHeight="1" spans="1:9">
       <c r="A289" s="2" t="s">
         <v>560</v>
       </c>
@@ -9526,16 +10394,16 @@
         <v>23</v>
       </c>
       <c r="F289" s="2">
-        <v>300.0</v>
+        <v>300</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I289" s="2">
-        <v>79.0</v>
-      </c>
-    </row>
-    <row r="290" ht="14.25" customHeight="1">
+      <c r="I289" s="4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="290" ht="14.25" customHeight="1" spans="1:9">
       <c r="A290" s="2" t="s">
         <v>560</v>
       </c>
@@ -9552,16 +10420,16 @@
         <v>13</v>
       </c>
       <c r="F290" s="2">
-        <v>15000.0</v>
+        <v>15000</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I290" s="2">
-        <v>2925.0</v>
-      </c>
-    </row>
-    <row r="291" ht="14.25" customHeight="1">
+      <c r="I290" s="4">
+        <v>2902</v>
+      </c>
+    </row>
+    <row r="291" ht="14.25" customHeight="1" spans="1:9">
       <c r="A291" s="2" t="s">
         <v>563</v>
       </c>
@@ -9578,16 +10446,16 @@
         <v>13</v>
       </c>
       <c r="F291" s="2">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I291" s="2">
-        <v>45.0</v>
-      </c>
-    </row>
-    <row r="292" ht="14.25" customHeight="1">
+      <c r="I291" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="292" ht="14.25" customHeight="1" spans="1:9">
       <c r="A292" s="2" t="s">
         <v>566</v>
       </c>
@@ -9604,16 +10472,16 @@
         <v>13</v>
       </c>
       <c r="F292" s="2">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I292" s="2">
-        <v>83.0</v>
-      </c>
-    </row>
-    <row r="293" ht="14.25" customHeight="1">
+      <c r="I292" s="4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="293" ht="14.25" customHeight="1" spans="1:9">
       <c r="A293" s="2" t="s">
         <v>568</v>
       </c>
@@ -9630,16 +10498,16 @@
         <v>13</v>
       </c>
       <c r="F293" s="2">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I293" s="2">
-        <v>195.0</v>
-      </c>
-    </row>
-    <row r="294" ht="14.25" customHeight="1">
+      <c r="I293" s="4">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="294" ht="14.25" customHeight="1" spans="1:9">
       <c r="A294" s="2" t="s">
         <v>568</v>
       </c>
@@ -9656,13 +10524,13 @@
         <v>13</v>
       </c>
       <c r="F294" s="2">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I294" s="2">
-        <v>978.0</v>
+      <c r="I294" s="4">
+        <v>94</v>
       </c>
     </row>
     <row r="295" ht="14.25" customHeight="1"/>
@@ -10372,9 +11240,8 @@
     <row r="999" ht="14.25" customHeight="1"/>
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="1" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>